--- a/Region_data_UD.xlsx
+++ b/Region_data_UD.xlsx
@@ -20,6 +20,8 @@
     <sheet name="Carlisle_NS" sheetId="13" r:id="rId15"/>
     <sheet name="Stafford_operators" sheetId="14" r:id="rId16"/>
     <sheet name="Stafford_NS" sheetId="15" r:id="rId17"/>
+    <sheet name="Scotland_operators" sheetId="16" r:id="rId18"/>
+    <sheet name="Scotland_NS" sheetId="17" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
@@ -27,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="835" uniqueCount="422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1303" uniqueCount="628">
   <si>
     <t>Name</t>
   </si>
@@ -1293,6 +1295,624 @@
   </si>
   <si>
     <t>G16</t>
+  </si>
+  <si>
+    <t>Alan Anderson</t>
+  </si>
+  <si>
+    <t>Alasdair Lannigan</t>
+  </si>
+  <si>
+    <t>Gillian Crisp</t>
+  </si>
+  <si>
+    <t>Sean O'Neill</t>
+  </si>
+  <si>
+    <t>Ryan Leggat</t>
+  </si>
+  <si>
+    <t>William Kenny</t>
+  </si>
+  <si>
+    <t>John Goodyear</t>
+  </si>
+  <si>
+    <t>Henry Ewart</t>
+  </si>
+  <si>
+    <t>Steven Dunn</t>
+  </si>
+  <si>
+    <t>Graeme Beattie</t>
+  </si>
+  <si>
+    <t>Gary Henderson</t>
+  </si>
+  <si>
+    <t>aa</t>
+  </si>
+  <si>
+    <t>al</t>
+  </si>
+  <si>
+    <t>gc</t>
+  </si>
+  <si>
+    <t>so</t>
+  </si>
+  <si>
+    <t>rl</t>
+  </si>
+  <si>
+    <t>wk</t>
+  </si>
+  <si>
+    <t>he</t>
+  </si>
+  <si>
+    <t>sd</t>
+  </si>
+  <si>
+    <t>gb</t>
+  </si>
+  <si>
+    <t>gh</t>
+  </si>
+  <si>
+    <t>Bathgate Fs</t>
+  </si>
+  <si>
+    <t>Bellgrove Junction</t>
+  </si>
+  <si>
+    <t>Carmuirs Junction</t>
+  </si>
+  <si>
+    <t>Carstairs</t>
+  </si>
+  <si>
+    <t>Drumgelloch</t>
+  </si>
+  <si>
+    <t>Ecclefechan</t>
+  </si>
+  <si>
+    <t>Elvanfoot</t>
+  </si>
+  <si>
+    <t>Ferguslie Fs</t>
+  </si>
+  <si>
+    <t>Finnieston</t>
+  </si>
+  <si>
+    <t>Garnqueen</t>
+  </si>
+  <si>
+    <t>Gartcosh</t>
+  </si>
+  <si>
+    <t>Gowkthrapple</t>
+  </si>
+  <si>
+    <t>Greenhill Fs</t>
+  </si>
+  <si>
+    <t>Greenhill Lwr Junction</t>
+  </si>
+  <si>
+    <t>Grhmston</t>
+  </si>
+  <si>
+    <t>Haymarket</t>
+  </si>
+  <si>
+    <t>Holytown Jn</t>
+  </si>
+  <si>
+    <t>Kincardine</t>
+  </si>
+  <si>
+    <t>Kirkhill</t>
+  </si>
+  <si>
+    <t>Langloan Junction</t>
+  </si>
+  <si>
+    <t>Midcalder Junction</t>
+  </si>
+  <si>
+    <t>Muirhouse Jn</t>
+  </si>
+  <si>
+    <t>Murthat</t>
+  </si>
+  <si>
+    <t>Musselburgh</t>
+  </si>
+  <si>
+    <t>Newbridge</t>
+  </si>
+  <si>
+    <t>Newton</t>
+  </si>
+  <si>
+    <t>Parkhead</t>
+  </si>
+  <si>
+    <t>Perth</t>
+  </si>
+  <si>
+    <t>Polmont Junction</t>
+  </si>
+  <si>
+    <t>Rutherglen</t>
+  </si>
+  <si>
+    <t>Shields Junction</t>
+  </si>
+  <si>
+    <t>Sighthill</t>
+  </si>
+  <si>
+    <t>Slateford</t>
+  </si>
+  <si>
+    <t>Stirling Bridge</t>
+  </si>
+  <si>
+    <t>Reversible Slow(Csp)</t>
+  </si>
+  <si>
+    <t>Reversible Fast(Csp)</t>
+  </si>
+  <si>
+    <t>Up Main G(Wcm1)</t>
+  </si>
+  <si>
+    <t>Down Main G(Wcm1)</t>
+  </si>
+  <si>
+    <t>Up Main Ge(Eca1)</t>
+  </si>
+  <si>
+    <t>Down Main Ge(Eca1)</t>
+  </si>
+  <si>
+    <t>Argyle Down Main</t>
+  </si>
+  <si>
+    <t>Up Main(Nem3)</t>
+  </si>
+  <si>
+    <t>Down Main(Nem3)</t>
+  </si>
+  <si>
+    <t>Up Main(North)</t>
+  </si>
+  <si>
+    <t>Down Main(North)</t>
+  </si>
+  <si>
+    <t>Up Main(Junction)</t>
+  </si>
+  <si>
+    <t>Down Main(Junction)</t>
+  </si>
+  <si>
+    <t>Bi Dir Single</t>
+  </si>
+  <si>
+    <t>Up Main(Scm3)</t>
+  </si>
+  <si>
+    <t>Down Main(Scm3)</t>
+  </si>
+  <si>
+    <t>Up Main(Ghl)</t>
+  </si>
+  <si>
+    <t>Down Main(Ghl)</t>
+  </si>
+  <si>
+    <t>Up Main (Wwd)</t>
+  </si>
+  <si>
+    <t>Down Main (Wwd)</t>
+  </si>
+  <si>
+    <t>Up Main (Egs)</t>
+  </si>
+  <si>
+    <t>Down Main (Egs)</t>
+  </si>
+  <si>
+    <t>Up Main (Rsl1)</t>
+  </si>
+  <si>
+    <t>Down Main (Rsl1)</t>
+  </si>
+  <si>
+    <t>Up Main (Rcb1)</t>
+  </si>
+  <si>
+    <t>Down Main (Rcb1)</t>
+  </si>
+  <si>
+    <t>Up Main(Bak)</t>
+  </si>
+  <si>
+    <t>Down Main(Bak)</t>
+  </si>
+  <si>
+    <t>Up Main(Ctc)</t>
+  </si>
+  <si>
+    <t>Down Main(Ctc)</t>
+  </si>
+  <si>
+    <t>Up Main(Nbe)</t>
+  </si>
+  <si>
+    <t>Down Main(Nbe)</t>
+  </si>
+  <si>
+    <t>Down Slow (West)</t>
+  </si>
+  <si>
+    <t>Ross-East</t>
+  </si>
+  <si>
+    <t>Curve (Bi Dir Single)</t>
+  </si>
+  <si>
+    <t>Up Main(Ayr)</t>
+  </si>
+  <si>
+    <t>Down Main(Ayr)</t>
+  </si>
+  <si>
+    <t>Up Main(City Union)</t>
+  </si>
+  <si>
+    <t>Down Main(City Union)</t>
+  </si>
+  <si>
+    <t>F/31/32</t>
+  </si>
+  <si>
+    <t>FS/00/02B</t>
+  </si>
+  <si>
+    <t>GDC/00/03A</t>
+  </si>
+  <si>
+    <t>GEN/00/16</t>
+  </si>
+  <si>
+    <t>G/599/42A</t>
+  </si>
+  <si>
+    <t>G599/17A</t>
+  </si>
+  <si>
+    <t>GES/00/09</t>
+  </si>
+  <si>
+    <t>GES/00/08</t>
+  </si>
+  <si>
+    <t>F/12/31</t>
+  </si>
+  <si>
+    <t>G/513/3</t>
+  </si>
+  <si>
+    <t>G/566/04</t>
+  </si>
+  <si>
+    <t>G/566/03</t>
+  </si>
+  <si>
+    <t>LA/02/14</t>
+  </si>
+  <si>
+    <t>B/02/05</t>
+  </si>
+  <si>
+    <t>GD/12/04</t>
+  </si>
+  <si>
+    <t>FT/11/28</t>
+  </si>
+  <si>
+    <t>FX/00/16</t>
+  </si>
+  <si>
+    <t>G/619/34</t>
+  </si>
+  <si>
+    <t>G/619/33</t>
+  </si>
+  <si>
+    <t>EG/28/19</t>
+  </si>
+  <si>
+    <t>GD/28/09</t>
+  </si>
+  <si>
+    <t>GD/32/34</t>
+  </si>
+  <si>
+    <t>PC2K</t>
+  </si>
+  <si>
+    <t>CH5B</t>
+  </si>
+  <si>
+    <t>GL/4/04</t>
+  </si>
+  <si>
+    <t>GL/3/04</t>
+  </si>
+  <si>
+    <t>GL5/03</t>
+  </si>
+  <si>
+    <t>GL6/5F</t>
+  </si>
+  <si>
+    <t>ES/01/20</t>
+  </si>
+  <si>
+    <t>GK04/50A</t>
+  </si>
+  <si>
+    <t>GF/10/28</t>
+  </si>
+  <si>
+    <t>GG/00/07</t>
+  </si>
+  <si>
+    <t>GG/00/08</t>
+  </si>
+  <si>
+    <t>GL7/04</t>
+  </si>
+  <si>
+    <t>GL7/05</t>
+  </si>
+  <si>
+    <t>K/00/20</t>
+  </si>
+  <si>
+    <t>K00/20</t>
+  </si>
+  <si>
+    <t>G/540/26</t>
+  </si>
+  <si>
+    <t>G/540/25</t>
+  </si>
+  <si>
+    <t>E626/22A</t>
+  </si>
+  <si>
+    <t>RN3G</t>
+  </si>
+  <si>
+    <t>RN4A</t>
+  </si>
+  <si>
+    <t>BH3</t>
+  </si>
+  <si>
+    <t>CH6G/BH4</t>
+  </si>
+  <si>
+    <t>G/636/17</t>
+  </si>
+  <si>
+    <t>GK04/04A</t>
+  </si>
+  <si>
+    <t>F/01/41</t>
+  </si>
+  <si>
+    <t>EP/00/20</t>
+  </si>
+  <si>
+    <t>EP/00/21</t>
+  </si>
+  <si>
+    <t>RW/0/16</t>
+  </si>
+  <si>
+    <t>L00/100A</t>
+  </si>
+  <si>
+    <t>FT/00/04</t>
+  </si>
+  <si>
+    <t>GE/42/10A</t>
+  </si>
+  <si>
+    <t>GD/48/13</t>
+  </si>
+  <si>
+    <t>NEM1</t>
+  </si>
+  <si>
+    <t>SGN</t>
+  </si>
+  <si>
+    <t>CMS</t>
+  </si>
+  <si>
+    <t>CSP</t>
+  </si>
+  <si>
+    <t>ECA1</t>
+  </si>
+  <si>
+    <t>NEM2</t>
+  </si>
+  <si>
+    <t>AYR3</t>
+  </si>
+  <si>
+    <t>ARG2</t>
+  </si>
+  <si>
+    <t>NEM3</t>
+  </si>
+  <si>
+    <t>SCM3</t>
+  </si>
+  <si>
+    <t>CBD1</t>
+  </si>
+  <si>
+    <t>GHE</t>
+  </si>
+  <si>
+    <t>WCM2</t>
+  </si>
+  <si>
+    <t>EGM1</t>
+  </si>
+  <si>
+    <t>GHL</t>
+  </si>
+  <si>
+    <t>PMT</t>
+  </si>
+  <si>
+    <t>EGM2</t>
+  </si>
+  <si>
+    <t>WWD</t>
+  </si>
+  <si>
+    <t>EGS2</t>
+  </si>
+  <si>
+    <t>SAA</t>
+  </si>
+  <si>
+    <t>KHL</t>
+  </si>
+  <si>
+    <t>RSL1</t>
+  </si>
+  <si>
+    <t>RCB</t>
+  </si>
+  <si>
+    <t>MEN2</t>
+  </si>
+  <si>
+    <t>CTC</t>
+  </si>
+  <si>
+    <t>ECM8</t>
+  </si>
+  <si>
+    <t>NBE</t>
+  </si>
+  <si>
+    <t>HMN2</t>
+  </si>
+  <si>
+    <t>RNC</t>
+  </si>
+  <si>
+    <t>AYR1</t>
+  </si>
+  <si>
+    <t>HST</t>
+  </si>
+  <si>
+    <t>CBD2</t>
+  </si>
+  <si>
+    <t>ECA3</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>FS</t>
+  </si>
+  <si>
+    <t>GDC</t>
+  </si>
+  <si>
+    <t>GE</t>
+  </si>
+  <si>
+    <t>GEN</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>LA</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>GD</t>
+  </si>
+  <si>
+    <t>FT</t>
+  </si>
+  <si>
+    <t>FX</t>
+  </si>
+  <si>
+    <t>GK</t>
+  </si>
+  <si>
+    <t>EG</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>GM</t>
+  </si>
+  <si>
+    <t>GT</t>
+  </si>
+  <si>
+    <t>ES</t>
+  </si>
+  <si>
+    <t>GF</t>
+  </si>
+  <si>
+    <t>GG</t>
+  </si>
+  <si>
+    <t>EK</t>
+  </si>
+  <si>
+    <t>K</t>
+  </si>
+  <si>
+    <t>GC</t>
+  </si>
+  <si>
+    <t>GH</t>
+  </si>
+  <si>
+    <t>EP</t>
+  </si>
+  <si>
+    <t>RW</t>
   </si>
 </sst>
 </file>
@@ -3464,6 +4084,2494 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="16.5703125" customWidth="true"/>
+    <col min="2" max="2" width="8.42578125" customWidth="true"/>
+    <col min="3" max="3" width="5.85546875" customWidth="true"/>
+    <col min="4" max="4" width="4.140625" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="s">
+        <v>422</v>
+      </c>
+      <c r="B2" s="0">
+        <v>1161419</v>
+      </c>
+      <c r="C2" s="0">
+        <v>1</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="s">
+        <v>423</v>
+      </c>
+      <c r="B3" s="0">
+        <v>1317648</v>
+      </c>
+      <c r="C3" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="s">
+        <v>424</v>
+      </c>
+      <c r="B4" s="0">
+        <v>1349812</v>
+      </c>
+      <c r="C4" s="0">
+        <v>1</v>
+      </c>
+      <c r="D4" s="0" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="s">
+        <v>425</v>
+      </c>
+      <c r="B5" s="0">
+        <v>1372275</v>
+      </c>
+      <c r="C5" s="0">
+        <v>1</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="s">
+        <v>426</v>
+      </c>
+      <c r="B6" s="0">
+        <v>1218733</v>
+      </c>
+      <c r="C6" s="0">
+        <v>1</v>
+      </c>
+      <c r="D6" s="0" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="s">
+        <v>427</v>
+      </c>
+      <c r="B7" s="0">
+        <v>574535</v>
+      </c>
+      <c r="C7" s="0">
+        <v>1</v>
+      </c>
+      <c r="D7" s="0" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="s">
+        <v>428</v>
+      </c>
+      <c r="B8" s="0">
+        <v>120340</v>
+      </c>
+      <c r="C8" s="0">
+        <v>1</v>
+      </c>
+      <c r="D8" s="0" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="s">
+        <v>429</v>
+      </c>
+      <c r="B9" s="0">
+        <v>120212</v>
+      </c>
+      <c r="C9" s="0">
+        <v>1</v>
+      </c>
+      <c r="D9" s="0" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="s">
+        <v>430</v>
+      </c>
+      <c r="B10" s="0">
+        <v>622047</v>
+      </c>
+      <c r="C10" s="0">
+        <v>1</v>
+      </c>
+      <c r="D10" s="0" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="s">
+        <v>431</v>
+      </c>
+      <c r="B11" s="0">
+        <v>574509</v>
+      </c>
+      <c r="C11" s="0">
+        <v>1</v>
+      </c>
+      <c r="D11" s="0" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="s">
+        <v>432</v>
+      </c>
+      <c r="B12" s="0">
+        <v>590336</v>
+      </c>
+      <c r="C12" s="0">
+        <v>1</v>
+      </c>
+      <c r="D12" s="0" t="s">
+        <v>442</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H88"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="21.85546875" customWidth="true"/>
+    <col min="2" max="2" width="21.7109375" customWidth="true"/>
+    <col min="3" max="3" width="8.28515625" customWidth="true"/>
+    <col min="4" max="4" width="9.5703125" customWidth="true"/>
+    <col min="5" max="5" width="11.85546875" customWidth="true"/>
+    <col min="6" max="6" width="6.85546875" customWidth="true"/>
+    <col min="7" max="7" width="17.42578125" customWidth="true"/>
+    <col min="8" max="8" width="14.28515625" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="G1" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="H1" s="0" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="s">
+        <v>443</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>277</v>
+      </c>
+      <c r="C2" s="0">
+        <v>1100</v>
+      </c>
+      <c r="D2" s="0">
+        <v>107</v>
+      </c>
+      <c r="E2" s="0" t="s">
+        <v>516</v>
+      </c>
+      <c r="F2" s="0" t="s">
+        <v>570</v>
+      </c>
+      <c r="G2" s="0" t="s">
+        <v>603</v>
+      </c>
+      <c r="H2" s="0">
+        <v>6737415</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="s">
+        <v>443</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>278</v>
+      </c>
+      <c r="C3" s="0">
+        <v>2100</v>
+      </c>
+      <c r="D3" s="0">
+        <v>107</v>
+      </c>
+      <c r="E3" s="0" t="s">
+        <v>516</v>
+      </c>
+      <c r="F3" s="0" t="s">
+        <v>570</v>
+      </c>
+      <c r="G3" s="0" t="s">
+        <v>603</v>
+      </c>
+      <c r="H3" s="0">
+        <v>6737416</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="s">
+        <v>444</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>277</v>
+      </c>
+      <c r="C4" s="0">
+        <v>1100</v>
+      </c>
+      <c r="D4" s="0">
+        <v>107</v>
+      </c>
+      <c r="E4" s="0" t="s">
+        <v>517</v>
+      </c>
+      <c r="F4" s="0" t="s">
+        <v>571</v>
+      </c>
+      <c r="G4" s="0" t="s">
+        <v>604</v>
+      </c>
+      <c r="H4" s="0">
+        <v>18771404</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="s">
+        <v>444</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>278</v>
+      </c>
+      <c r="C5" s="0">
+        <v>2100</v>
+      </c>
+      <c r="D5" s="0">
+        <v>107</v>
+      </c>
+      <c r="E5" s="0" t="s">
+        <v>517</v>
+      </c>
+      <c r="F5" s="0" t="s">
+        <v>571</v>
+      </c>
+      <c r="G5" s="0" t="s">
+        <v>604</v>
+      </c>
+      <c r="H5" s="0">
+        <v>18771405</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="s">
+        <v>445</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>277</v>
+      </c>
+      <c r="C6" s="0">
+        <v>1100</v>
+      </c>
+      <c r="D6" s="0">
+        <v>107</v>
+      </c>
+      <c r="E6" s="0" t="s">
+        <v>518</v>
+      </c>
+      <c r="F6" s="0" t="s">
+        <v>572</v>
+      </c>
+      <c r="G6" s="0" t="s">
+        <v>605</v>
+      </c>
+      <c r="H6" s="0">
+        <v>18839472</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="s">
+        <v>445</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>278</v>
+      </c>
+      <c r="C7" s="0">
+        <v>2100</v>
+      </c>
+      <c r="D7" s="0">
+        <v>107</v>
+      </c>
+      <c r="E7" s="0" t="s">
+        <v>518</v>
+      </c>
+      <c r="F7" s="0" t="s">
+        <v>572</v>
+      </c>
+      <c r="G7" s="0" t="s">
+        <v>605</v>
+      </c>
+      <c r="H7" s="0">
+        <v>18839473</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="s">
+        <v>446</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>477</v>
+      </c>
+      <c r="C8" s="0">
+        <v>3200</v>
+      </c>
+      <c r="D8" s="0">
+        <v>107</v>
+      </c>
+      <c r="E8" s="0" t="s">
+        <v>519</v>
+      </c>
+      <c r="F8" s="0" t="s">
+        <v>573</v>
+      </c>
+      <c r="G8" s="0" t="s">
+        <v>606</v>
+      </c>
+      <c r="H8" s="0">
+        <v>677079</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="s">
+        <v>446</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>478</v>
+      </c>
+      <c r="C9" s="0">
+        <v>3100</v>
+      </c>
+      <c r="D9" s="0">
+        <v>107</v>
+      </c>
+      <c r="E9" s="0" t="s">
+        <v>520</v>
+      </c>
+      <c r="F9" s="0" t="s">
+        <v>573</v>
+      </c>
+      <c r="G9" s="0" t="s">
+        <v>607</v>
+      </c>
+      <c r="H9" s="0">
+        <v>677113</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="s">
+        <v>446</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>479</v>
+      </c>
+      <c r="C10" s="0">
+        <v>1100</v>
+      </c>
+      <c r="D10" s="0">
+        <v>107</v>
+      </c>
+      <c r="E10" s="0" t="s">
+        <v>521</v>
+      </c>
+      <c r="F10" s="0" t="s">
+        <v>353</v>
+      </c>
+      <c r="G10" s="0" t="s">
+        <v>608</v>
+      </c>
+      <c r="H10" s="0">
+        <v>677168</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="s">
+        <v>446</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>480</v>
+      </c>
+      <c r="C11" s="0">
+        <v>2100</v>
+      </c>
+      <c r="D11" s="0">
+        <v>107</v>
+      </c>
+      <c r="E11" s="0" t="s">
+        <v>521</v>
+      </c>
+      <c r="F11" s="0" t="s">
+        <v>353</v>
+      </c>
+      <c r="G11" s="0" t="s">
+        <v>608</v>
+      </c>
+      <c r="H11" s="0">
+        <v>677140</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="s">
+        <v>446</v>
+      </c>
+      <c r="B12" s="0" t="s">
+        <v>481</v>
+      </c>
+      <c r="C12" s="0">
+        <v>1100</v>
+      </c>
+      <c r="D12" s="0">
+        <v>107</v>
+      </c>
+      <c r="E12" s="0" t="s">
+        <v>522</v>
+      </c>
+      <c r="F12" s="0" t="s">
+        <v>574</v>
+      </c>
+      <c r="G12" s="0" t="s">
+        <v>606</v>
+      </c>
+      <c r="H12" s="0">
+        <v>677149</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="s">
+        <v>446</v>
+      </c>
+      <c r="B13" s="0" t="s">
+        <v>482</v>
+      </c>
+      <c r="C13" s="0">
+        <v>2100</v>
+      </c>
+      <c r="D13" s="0">
+        <v>107</v>
+      </c>
+      <c r="E13" s="0" t="s">
+        <v>523</v>
+      </c>
+      <c r="F13" s="0" t="s">
+        <v>574</v>
+      </c>
+      <c r="G13" s="0" t="s">
+        <v>606</v>
+      </c>
+      <c r="H13" s="0">
+        <v>677148</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="s">
+        <v>447</v>
+      </c>
+      <c r="B14" s="0" t="s">
+        <v>277</v>
+      </c>
+      <c r="C14" s="0">
+        <v>1100</v>
+      </c>
+      <c r="D14" s="0">
+        <v>107</v>
+      </c>
+      <c r="E14" s="0" t="s">
+        <v>524</v>
+      </c>
+      <c r="F14" s="0" t="s">
+        <v>575</v>
+      </c>
+      <c r="G14" s="0" t="s">
+        <v>603</v>
+      </c>
+      <c r="H14" s="0">
+        <v>6737419</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="s">
+        <v>447</v>
+      </c>
+      <c r="B15" s="0" t="s">
+        <v>278</v>
+      </c>
+      <c r="C15" s="0">
+        <v>2100</v>
+      </c>
+      <c r="D15" s="0">
+        <v>107</v>
+      </c>
+      <c r="E15" s="0" t="s">
+        <v>524</v>
+      </c>
+      <c r="F15" s="0" t="s">
+        <v>575</v>
+      </c>
+      <c r="G15" s="0" t="s">
+        <v>603</v>
+      </c>
+      <c r="H15" s="0">
+        <v>6737420</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0" t="s">
+        <v>448</v>
+      </c>
+      <c r="B16" s="0" t="s">
+        <v>277</v>
+      </c>
+      <c r="C16" s="0">
+        <v>1100</v>
+      </c>
+      <c r="D16" s="0">
+        <v>107</v>
+      </c>
+      <c r="E16" s="0" t="s">
+        <v>525</v>
+      </c>
+      <c r="F16" s="0" t="s">
+        <v>353</v>
+      </c>
+      <c r="G16" s="0" t="s">
+        <v>608</v>
+      </c>
+      <c r="H16" s="0">
+        <v>677105</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0" t="s">
+        <v>448</v>
+      </c>
+      <c r="B17" s="0" t="s">
+        <v>278</v>
+      </c>
+      <c r="C17" s="0">
+        <v>2100</v>
+      </c>
+      <c r="D17" s="0">
+        <v>107</v>
+      </c>
+      <c r="E17" s="0" t="s">
+        <v>525</v>
+      </c>
+      <c r="F17" s="0" t="s">
+        <v>353</v>
+      </c>
+      <c r="G17" s="0" t="s">
+        <v>608</v>
+      </c>
+      <c r="H17" s="0">
+        <v>677114</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="0" t="s">
+        <v>449</v>
+      </c>
+      <c r="B18" s="0" t="s">
+        <v>277</v>
+      </c>
+      <c r="C18" s="0">
+        <v>1100</v>
+      </c>
+      <c r="D18" s="0">
+        <v>107</v>
+      </c>
+      <c r="E18" s="0" t="s">
+        <v>526</v>
+      </c>
+      <c r="F18" s="0" t="s">
+        <v>353</v>
+      </c>
+      <c r="G18" s="0" t="s">
+        <v>608</v>
+      </c>
+      <c r="H18" s="0">
+        <v>677153</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="0" t="s">
+        <v>449</v>
+      </c>
+      <c r="B19" s="0" t="s">
+        <v>278</v>
+      </c>
+      <c r="C19" s="0">
+        <v>2100</v>
+      </c>
+      <c r="D19" s="0">
+        <v>107</v>
+      </c>
+      <c r="E19" s="0" t="s">
+        <v>527</v>
+      </c>
+      <c r="F19" s="0" t="s">
+        <v>353</v>
+      </c>
+      <c r="G19" s="0" t="s">
+        <v>608</v>
+      </c>
+      <c r="H19" s="0">
+        <v>677124</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="0" t="s">
+        <v>450</v>
+      </c>
+      <c r="B20" s="0" t="s">
+        <v>277</v>
+      </c>
+      <c r="C20" s="0">
+        <v>1100</v>
+      </c>
+      <c r="D20" s="0">
+        <v>107</v>
+      </c>
+      <c r="E20" s="0" t="s">
+        <v>528</v>
+      </c>
+      <c r="F20" s="0" t="s">
+        <v>576</v>
+      </c>
+      <c r="G20" s="0" t="s">
+        <v>609</v>
+      </c>
+      <c r="H20" s="0">
+        <v>19470810</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="s">
+        <v>450</v>
+      </c>
+      <c r="B21" s="0" t="s">
+        <v>278</v>
+      </c>
+      <c r="C21" s="0">
+        <v>2100</v>
+      </c>
+      <c r="D21" s="0">
+        <v>107</v>
+      </c>
+      <c r="E21" s="0" t="s">
+        <v>528</v>
+      </c>
+      <c r="F21" s="0" t="s">
+        <v>576</v>
+      </c>
+      <c r="G21" s="0" t="s">
+        <v>609</v>
+      </c>
+      <c r="H21" s="0">
+        <v>19470811</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="0" t="s">
+        <v>451</v>
+      </c>
+      <c r="B22" s="0" t="s">
+        <v>483</v>
+      </c>
+      <c r="C22" s="0">
+        <v>2100</v>
+      </c>
+      <c r="D22" s="0">
+        <v>107</v>
+      </c>
+      <c r="E22" s="0" t="s">
+        <v>529</v>
+      </c>
+      <c r="F22" s="0" t="s">
+        <v>577</v>
+      </c>
+      <c r="G22" s="0" t="s">
+        <v>610</v>
+      </c>
+      <c r="H22" s="0">
+        <v>677138</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="0" t="s">
+        <v>451</v>
+      </c>
+      <c r="B23" s="0" t="s">
+        <v>484</v>
+      </c>
+      <c r="C23" s="0">
+        <v>1100</v>
+      </c>
+      <c r="D23" s="0">
+        <v>107</v>
+      </c>
+      <c r="E23" s="0" t="s">
+        <v>529</v>
+      </c>
+      <c r="F23" s="0" t="s">
+        <v>578</v>
+      </c>
+      <c r="G23" s="0" t="s">
+        <v>610</v>
+      </c>
+      <c r="H23" s="0">
+        <v>677141</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="0" t="s">
+        <v>451</v>
+      </c>
+      <c r="B24" s="0" t="s">
+        <v>485</v>
+      </c>
+      <c r="C24" s="0">
+        <v>2100</v>
+      </c>
+      <c r="D24" s="0">
+        <v>107</v>
+      </c>
+      <c r="E24" s="0" t="s">
+        <v>529</v>
+      </c>
+      <c r="F24" s="0" t="s">
+        <v>578</v>
+      </c>
+      <c r="G24" s="0" t="s">
+        <v>610</v>
+      </c>
+      <c r="H24" s="0">
+        <v>677150</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0" t="s">
+        <v>452</v>
+      </c>
+      <c r="B25" s="0" t="s">
+        <v>486</v>
+      </c>
+      <c r="C25" s="0">
+        <v>1100</v>
+      </c>
+      <c r="D25" s="0">
+        <v>107</v>
+      </c>
+      <c r="E25" s="0" t="s">
+        <v>530</v>
+      </c>
+      <c r="F25" s="0" t="s">
+        <v>579</v>
+      </c>
+      <c r="G25" s="0" t="s">
+        <v>611</v>
+      </c>
+      <c r="H25" s="0">
+        <v>9697138</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="s">
+        <v>452</v>
+      </c>
+      <c r="B26" s="0" t="s">
+        <v>487</v>
+      </c>
+      <c r="C26" s="0">
+        <v>2100</v>
+      </c>
+      <c r="D26" s="0">
+        <v>107</v>
+      </c>
+      <c r="E26" s="0" t="s">
+        <v>530</v>
+      </c>
+      <c r="F26" s="0" t="s">
+        <v>579</v>
+      </c>
+      <c r="G26" s="0" t="s">
+        <v>611</v>
+      </c>
+      <c r="H26" s="0">
+        <v>9697137</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="s">
+        <v>452</v>
+      </c>
+      <c r="B27" s="0" t="s">
+        <v>488</v>
+      </c>
+      <c r="C27" s="0">
+        <v>1100</v>
+      </c>
+      <c r="D27" s="0">
+        <v>107</v>
+      </c>
+      <c r="E27" s="0" t="s">
+        <v>531</v>
+      </c>
+      <c r="F27" s="0" t="s">
+        <v>580</v>
+      </c>
+      <c r="G27" s="0" t="s">
+        <v>612</v>
+      </c>
+      <c r="H27" s="0">
+        <v>18772023</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="s">
+        <v>452</v>
+      </c>
+      <c r="B28" s="0" t="s">
+        <v>489</v>
+      </c>
+      <c r="C28" s="0">
+        <v>2100</v>
+      </c>
+      <c r="D28" s="0">
+        <v>107</v>
+      </c>
+      <c r="E28" s="0" t="s">
+        <v>531</v>
+      </c>
+      <c r="F28" s="0" t="s">
+        <v>580</v>
+      </c>
+      <c r="G28" s="0" t="s">
+        <v>612</v>
+      </c>
+      <c r="H28" s="0">
+        <v>18772024</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="s">
+        <v>453</v>
+      </c>
+      <c r="B29" s="0" t="s">
+        <v>490</v>
+      </c>
+      <c r="C29" s="0">
+        <v>3400</v>
+      </c>
+      <c r="D29" s="0">
+        <v>107</v>
+      </c>
+      <c r="E29" s="0" t="s">
+        <v>532</v>
+      </c>
+      <c r="F29" s="0" t="s">
+        <v>581</v>
+      </c>
+      <c r="G29" s="0" t="s">
+        <v>613</v>
+      </c>
+      <c r="H29" s="0">
+        <v>18772025</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="0" t="s">
+        <v>454</v>
+      </c>
+      <c r="B30" s="0" t="s">
+        <v>277</v>
+      </c>
+      <c r="C30" s="0">
+        <v>1100</v>
+      </c>
+      <c r="D30" s="0">
+        <v>107</v>
+      </c>
+      <c r="E30" s="0" t="s">
+        <v>533</v>
+      </c>
+      <c r="F30" s="0" t="s">
+        <v>582</v>
+      </c>
+      <c r="G30" s="0" t="s">
+        <v>614</v>
+      </c>
+      <c r="H30" s="0">
+        <v>19289126</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="0" t="s">
+        <v>454</v>
+      </c>
+      <c r="B31" s="0" t="s">
+        <v>278</v>
+      </c>
+      <c r="C31" s="0">
+        <v>2100</v>
+      </c>
+      <c r="D31" s="0">
+        <v>107</v>
+      </c>
+      <c r="E31" s="0" t="s">
+        <v>534</v>
+      </c>
+      <c r="F31" s="0" t="s">
+        <v>582</v>
+      </c>
+      <c r="G31" s="0" t="s">
+        <v>608</v>
+      </c>
+      <c r="H31" s="0">
+        <v>19289125</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="0" t="s">
+        <v>455</v>
+      </c>
+      <c r="B32" s="0" t="s">
+        <v>277</v>
+      </c>
+      <c r="C32" s="0">
+        <v>1100</v>
+      </c>
+      <c r="D32" s="0">
+        <v>107</v>
+      </c>
+      <c r="E32" s="0" t="s">
+        <v>535</v>
+      </c>
+      <c r="F32" s="0" t="s">
+        <v>583</v>
+      </c>
+      <c r="G32" s="0" t="s">
+        <v>615</v>
+      </c>
+      <c r="H32" s="0">
+        <v>18748267</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="0" t="s">
+        <v>455</v>
+      </c>
+      <c r="B33" s="0" t="s">
+        <v>278</v>
+      </c>
+      <c r="C33" s="0">
+        <v>2100</v>
+      </c>
+      <c r="D33" s="0">
+        <v>107</v>
+      </c>
+      <c r="E33" s="0" t="s">
+        <v>535</v>
+      </c>
+      <c r="F33" s="0" t="s">
+        <v>583</v>
+      </c>
+      <c r="G33" s="0" t="s">
+        <v>615</v>
+      </c>
+      <c r="H33" s="0">
+        <v>18748268</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="0" t="s">
+        <v>456</v>
+      </c>
+      <c r="B34" s="0" t="s">
+        <v>491</v>
+      </c>
+      <c r="C34" s="0">
+        <v>1100</v>
+      </c>
+      <c r="D34" s="0">
+        <v>107</v>
+      </c>
+      <c r="E34" s="0" t="s">
+        <v>536</v>
+      </c>
+      <c r="F34" s="0" t="s">
+        <v>579</v>
+      </c>
+      <c r="G34" s="0" t="s">
+        <v>611</v>
+      </c>
+      <c r="H34" s="0">
+        <v>18748269</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="0" t="s">
+        <v>456</v>
+      </c>
+      <c r="B35" s="0" t="s">
+        <v>492</v>
+      </c>
+      <c r="C35" s="0">
+        <v>2100</v>
+      </c>
+      <c r="D35" s="0">
+        <v>107</v>
+      </c>
+      <c r="E35" s="0" t="s">
+        <v>536</v>
+      </c>
+      <c r="F35" s="0" t="s">
+        <v>579</v>
+      </c>
+      <c r="G35" s="0" t="s">
+        <v>611</v>
+      </c>
+      <c r="H35" s="0">
+        <v>18748270</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="0" t="s">
+        <v>456</v>
+      </c>
+      <c r="B36" s="0" t="s">
+        <v>493</v>
+      </c>
+      <c r="C36" s="0">
+        <v>1100</v>
+      </c>
+      <c r="D36" s="0">
+        <v>107</v>
+      </c>
+      <c r="E36" s="0" t="s">
+        <v>536</v>
+      </c>
+      <c r="F36" s="0" t="s">
+        <v>584</v>
+      </c>
+      <c r="G36" s="0" t="s">
+        <v>611</v>
+      </c>
+      <c r="H36" s="0">
+        <v>18748271</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="0" t="s">
+        <v>456</v>
+      </c>
+      <c r="B37" s="0" t="s">
+        <v>494</v>
+      </c>
+      <c r="C37" s="0">
+        <v>2100</v>
+      </c>
+      <c r="D37" s="0">
+        <v>107</v>
+      </c>
+      <c r="E37" s="0" t="s">
+        <v>536</v>
+      </c>
+      <c r="F37" s="0" t="s">
+        <v>584</v>
+      </c>
+      <c r="G37" s="0" t="s">
+        <v>611</v>
+      </c>
+      <c r="H37" s="0">
+        <v>18748272</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="0" t="s">
+        <v>457</v>
+      </c>
+      <c r="B38" s="0" t="s">
+        <v>277</v>
+      </c>
+      <c r="C38" s="0">
+        <v>1100</v>
+      </c>
+      <c r="D38" s="0">
+        <v>107</v>
+      </c>
+      <c r="E38" s="0" t="s">
+        <v>537</v>
+      </c>
+      <c r="F38" s="0" t="s">
+        <v>585</v>
+      </c>
+      <c r="G38" s="0" t="s">
+        <v>611</v>
+      </c>
+      <c r="H38" s="0">
+        <v>18905788</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="0" t="s">
+        <v>457</v>
+      </c>
+      <c r="B39" s="0" t="s">
+        <v>278</v>
+      </c>
+      <c r="C39" s="0">
+        <v>2100</v>
+      </c>
+      <c r="D39" s="0">
+        <v>107</v>
+      </c>
+      <c r="E39" s="0" t="s">
+        <v>537</v>
+      </c>
+      <c r="F39" s="0" t="s">
+        <v>585</v>
+      </c>
+      <c r="G39" s="0" t="s">
+        <v>611</v>
+      </c>
+      <c r="H39" s="0">
+        <v>18905787</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="0" t="s">
+        <v>458</v>
+      </c>
+      <c r="B40" s="0" t="s">
+        <v>277</v>
+      </c>
+      <c r="C40" s="0">
+        <v>1100</v>
+      </c>
+      <c r="D40" s="0">
+        <v>107</v>
+      </c>
+      <c r="E40" s="0" t="s">
+        <v>538</v>
+      </c>
+      <c r="F40" s="0" t="s">
+        <v>586</v>
+      </c>
+      <c r="G40" s="0" t="s">
+        <v>616</v>
+      </c>
+      <c r="H40" s="0">
+        <v>6737417</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="0" t="s">
+        <v>458</v>
+      </c>
+      <c r="B41" s="0" t="s">
+        <v>278</v>
+      </c>
+      <c r="C41" s="0">
+        <v>2100</v>
+      </c>
+      <c r="D41" s="0">
+        <v>107</v>
+      </c>
+      <c r="E41" s="0" t="s">
+        <v>539</v>
+      </c>
+      <c r="F41" s="0" t="s">
+        <v>586</v>
+      </c>
+      <c r="G41" s="0" t="s">
+        <v>616</v>
+      </c>
+      <c r="H41" s="0">
+        <v>6737418</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="0" t="s">
+        <v>459</v>
+      </c>
+      <c r="B42" s="0" t="s">
+        <v>495</v>
+      </c>
+      <c r="C42" s="0">
+        <v>1100</v>
+      </c>
+      <c r="D42" s="0">
+        <v>107</v>
+      </c>
+      <c r="E42" s="0" t="s">
+        <v>540</v>
+      </c>
+      <c r="F42" s="0" t="s">
+        <v>587</v>
+      </c>
+      <c r="G42" s="0" t="s">
+        <v>617</v>
+      </c>
+      <c r="H42" s="0">
+        <v>19044113</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="0" t="s">
+        <v>459</v>
+      </c>
+      <c r="B43" s="0" t="s">
+        <v>496</v>
+      </c>
+      <c r="C43" s="0">
+        <v>2100</v>
+      </c>
+      <c r="D43" s="0">
+        <v>107</v>
+      </c>
+      <c r="E43" s="0" t="s">
+        <v>541</v>
+      </c>
+      <c r="F43" s="0" t="s">
+        <v>587</v>
+      </c>
+      <c r="G43" s="0" t="s">
+        <v>618</v>
+      </c>
+      <c r="H43" s="0">
+        <v>19044114</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="0" t="s">
+        <v>459</v>
+      </c>
+      <c r="B44" s="0" t="s">
+        <v>497</v>
+      </c>
+      <c r="C44" s="0">
+        <v>1100</v>
+      </c>
+      <c r="D44" s="0">
+        <v>107</v>
+      </c>
+      <c r="E44" s="0" t="s">
+        <v>542</v>
+      </c>
+      <c r="F44" s="0" t="s">
+        <v>588</v>
+      </c>
+      <c r="G44" s="0" t="s">
+        <v>618</v>
+      </c>
+      <c r="H44" s="0">
+        <v>19044115</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="0" t="s">
+        <v>459</v>
+      </c>
+      <c r="B45" s="0" t="s">
+        <v>498</v>
+      </c>
+      <c r="C45" s="0">
+        <v>2100</v>
+      </c>
+      <c r="D45" s="0">
+        <v>107</v>
+      </c>
+      <c r="E45" s="0" t="s">
+        <v>543</v>
+      </c>
+      <c r="F45" s="0" t="s">
+        <v>588</v>
+      </c>
+      <c r="G45" s="0" t="s">
+        <v>608</v>
+      </c>
+      <c r="H45" s="0">
+        <v>19044116</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="0" t="s">
+        <v>460</v>
+      </c>
+      <c r="B46" s="0" t="s">
+        <v>277</v>
+      </c>
+      <c r="C46" s="0">
+        <v>1100</v>
+      </c>
+      <c r="D46" s="0">
+        <v>107</v>
+      </c>
+      <c r="E46" s="0" t="s">
+        <v>544</v>
+      </c>
+      <c r="F46" s="0" t="s">
+        <v>589</v>
+      </c>
+      <c r="G46" s="0" t="s">
+        <v>619</v>
+      </c>
+      <c r="H46" s="0">
+        <v>18905782</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="0" t="s">
+        <v>460</v>
+      </c>
+      <c r="B47" s="0" t="s">
+        <v>278</v>
+      </c>
+      <c r="C47" s="0">
+        <v>2100</v>
+      </c>
+      <c r="D47" s="0">
+        <v>107</v>
+      </c>
+      <c r="E47" s="0" t="s">
+        <v>544</v>
+      </c>
+      <c r="F47" s="0" t="s">
+        <v>589</v>
+      </c>
+      <c r="G47" s="0" t="s">
+        <v>619</v>
+      </c>
+      <c r="H47" s="0">
+        <v>18905781</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="0" t="s">
+        <v>461</v>
+      </c>
+      <c r="B48" s="0" t="s">
+        <v>277</v>
+      </c>
+      <c r="C48" s="0">
+        <v>1100</v>
+      </c>
+      <c r="D48" s="0">
+        <v>107</v>
+      </c>
+      <c r="E48" s="0" t="s">
+        <v>545</v>
+      </c>
+      <c r="F48" s="0" t="s">
+        <v>590</v>
+      </c>
+      <c r="G48" s="0" t="s">
+        <v>614</v>
+      </c>
+      <c r="H48" s="0">
+        <v>19865894</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="0" t="s">
+        <v>461</v>
+      </c>
+      <c r="B49" s="0" t="s">
+        <v>278</v>
+      </c>
+      <c r="C49" s="0">
+        <v>2100</v>
+      </c>
+      <c r="D49" s="0">
+        <v>107</v>
+      </c>
+      <c r="E49" s="0" t="s">
+        <v>545</v>
+      </c>
+      <c r="F49" s="0" t="s">
+        <v>590</v>
+      </c>
+      <c r="G49" s="0" t="s">
+        <v>614</v>
+      </c>
+      <c r="H49" s="0">
+        <v>19865893</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="0" t="s">
+        <v>462</v>
+      </c>
+      <c r="B50" s="0" t="s">
+        <v>499</v>
+      </c>
+      <c r="C50" s="0">
+        <v>1100</v>
+      </c>
+      <c r="D50" s="0">
+        <v>107</v>
+      </c>
+      <c r="E50" s="0" t="s">
+        <v>546</v>
+      </c>
+      <c r="F50" s="0" t="s">
+        <v>591</v>
+      </c>
+      <c r="G50" s="0" t="s">
+        <v>620</v>
+      </c>
+      <c r="H50" s="0">
+        <v>10367489</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="0" t="s">
+        <v>462</v>
+      </c>
+      <c r="B51" s="0" t="s">
+        <v>500</v>
+      </c>
+      <c r="C51" s="0">
+        <v>2100</v>
+      </c>
+      <c r="D51" s="0">
+        <v>107</v>
+      </c>
+      <c r="E51" s="0" t="s">
+        <v>546</v>
+      </c>
+      <c r="F51" s="0" t="s">
+        <v>591</v>
+      </c>
+      <c r="G51" s="0" t="s">
+        <v>620</v>
+      </c>
+      <c r="H51" s="0">
+        <v>10367490</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="0" t="s">
+        <v>462</v>
+      </c>
+      <c r="B52" s="0" t="s">
+        <v>501</v>
+      </c>
+      <c r="C52" s="0">
+        <v>1100</v>
+      </c>
+      <c r="D52" s="0">
+        <v>107</v>
+      </c>
+      <c r="E52" s="0" t="s">
+        <v>547</v>
+      </c>
+      <c r="F52" s="0" t="s">
+        <v>592</v>
+      </c>
+      <c r="G52" s="0" t="s">
+        <v>621</v>
+      </c>
+      <c r="H52" s="0">
+        <v>10367491</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="0" t="s">
+        <v>462</v>
+      </c>
+      <c r="B53" s="0" t="s">
+        <v>502</v>
+      </c>
+      <c r="C53" s="0">
+        <v>2100</v>
+      </c>
+      <c r="D53" s="0">
+        <v>107</v>
+      </c>
+      <c r="E53" s="0" t="s">
+        <v>548</v>
+      </c>
+      <c r="F53" s="0" t="s">
+        <v>592</v>
+      </c>
+      <c r="G53" s="0" t="s">
+        <v>621</v>
+      </c>
+      <c r="H53" s="0">
+        <v>10367492</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="0" t="s">
+        <v>463</v>
+      </c>
+      <c r="B54" s="0" t="s">
+        <v>277</v>
+      </c>
+      <c r="C54" s="0">
+        <v>1100</v>
+      </c>
+      <c r="D54" s="0">
+        <v>107</v>
+      </c>
+      <c r="E54" s="0" t="s">
+        <v>549</v>
+      </c>
+      <c r="F54" s="0" t="s">
+        <v>588</v>
+      </c>
+      <c r="G54" s="0" t="s">
+        <v>618</v>
+      </c>
+      <c r="H54" s="0">
+        <v>19044117</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="0" t="s">
+        <v>463</v>
+      </c>
+      <c r="B55" s="0" t="s">
+        <v>278</v>
+      </c>
+      <c r="C55" s="0">
+        <v>2100</v>
+      </c>
+      <c r="D55" s="0">
+        <v>107</v>
+      </c>
+      <c r="E55" s="0" t="s">
+        <v>550</v>
+      </c>
+      <c r="F55" s="0" t="s">
+        <v>588</v>
+      </c>
+      <c r="G55" s="0" t="s">
+        <v>618</v>
+      </c>
+      <c r="H55" s="0">
+        <v>19044118</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="0" t="s">
+        <v>464</v>
+      </c>
+      <c r="B56" s="0" t="s">
+        <v>503</v>
+      </c>
+      <c r="C56" s="0">
+        <v>1100</v>
+      </c>
+      <c r="D56" s="0">
+        <v>107</v>
+      </c>
+      <c r="E56" s="0" t="s">
+        <v>551</v>
+      </c>
+      <c r="F56" s="0" t="s">
+        <v>593</v>
+      </c>
+      <c r="G56" s="0" t="s">
+        <v>622</v>
+      </c>
+      <c r="H56" s="0">
+        <v>19926542</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="0" t="s">
+        <v>464</v>
+      </c>
+      <c r="B57" s="0" t="s">
+        <v>504</v>
+      </c>
+      <c r="C57" s="0">
+        <v>2100</v>
+      </c>
+      <c r="D57" s="0">
+        <v>107</v>
+      </c>
+      <c r="E57" s="0" t="s">
+        <v>551</v>
+      </c>
+      <c r="F57" s="0" t="s">
+        <v>593</v>
+      </c>
+      <c r="G57" s="0" t="s">
+        <v>623</v>
+      </c>
+      <c r="H57" s="0">
+        <v>19926545</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="0" t="s">
+        <v>464</v>
+      </c>
+      <c r="B58" s="0" t="s">
+        <v>505</v>
+      </c>
+      <c r="C58" s="0">
+        <v>2100</v>
+      </c>
+      <c r="D58" s="0">
+        <v>107</v>
+      </c>
+      <c r="E58" s="0" t="s">
+        <v>552</v>
+      </c>
+      <c r="F58" s="0" t="s">
+        <v>594</v>
+      </c>
+      <c r="G58" s="0" t="s">
+        <v>624</v>
+      </c>
+      <c r="H58" s="0">
+        <v>19926541</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="0" t="s">
+        <v>464</v>
+      </c>
+      <c r="B59" s="0" t="s">
+        <v>506</v>
+      </c>
+      <c r="C59" s="0">
+        <v>1100</v>
+      </c>
+      <c r="D59" s="0">
+        <v>107</v>
+      </c>
+      <c r="E59" s="0" t="s">
+        <v>552</v>
+      </c>
+      <c r="F59" s="0" t="s">
+        <v>594</v>
+      </c>
+      <c r="G59" s="0" t="s">
+        <v>623</v>
+      </c>
+      <c r="H59" s="0">
+        <v>19926543</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="0" t="s">
+        <v>465</v>
+      </c>
+      <c r="B60" s="0" t="s">
+        <v>277</v>
+      </c>
+      <c r="C60" s="0">
+        <v>1100</v>
+      </c>
+      <c r="D60" s="0">
+        <v>107</v>
+      </c>
+      <c r="E60" s="0" t="s">
+        <v>553</v>
+      </c>
+      <c r="F60" s="0" t="s">
+        <v>353</v>
+      </c>
+      <c r="G60" s="0" t="s">
+        <v>608</v>
+      </c>
+      <c r="H60" s="0">
+        <v>677155</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="0" t="s">
+        <v>465</v>
+      </c>
+      <c r="B61" s="0" t="s">
+        <v>278</v>
+      </c>
+      <c r="C61" s="0">
+        <v>2100</v>
+      </c>
+      <c r="D61" s="0">
+        <v>107</v>
+      </c>
+      <c r="E61" s="0" t="s">
+        <v>554</v>
+      </c>
+      <c r="F61" s="0" t="s">
+        <v>353</v>
+      </c>
+      <c r="G61" s="0" t="s">
+        <v>608</v>
+      </c>
+      <c r="H61" s="0">
+        <v>677154</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="0" t="s">
+        <v>466</v>
+      </c>
+      <c r="B62" s="0" t="s">
+        <v>277</v>
+      </c>
+      <c r="C62" s="0">
+        <v>1100</v>
+      </c>
+      <c r="D62" s="0">
+        <v>107</v>
+      </c>
+      <c r="E62" s="0" t="s">
+        <v>555</v>
+      </c>
+      <c r="F62" s="0" t="s">
+        <v>595</v>
+      </c>
+      <c r="G62" s="0" t="s">
+        <v>616</v>
+      </c>
+      <c r="H62" s="0">
+        <v>19982207</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="0" t="s">
+        <v>466</v>
+      </c>
+      <c r="B63" s="0" t="s">
+        <v>278</v>
+      </c>
+      <c r="C63" s="0">
+        <v>2100</v>
+      </c>
+      <c r="D63" s="0">
+        <v>107</v>
+      </c>
+      <c r="E63" s="0" t="s">
+        <v>555</v>
+      </c>
+      <c r="F63" s="0" t="s">
+        <v>595</v>
+      </c>
+      <c r="G63" s="0" t="s">
+        <v>616</v>
+      </c>
+      <c r="H63" s="0">
+        <v>19982210</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="0" t="s">
+        <v>467</v>
+      </c>
+      <c r="B64" s="0" t="s">
+        <v>488</v>
+      </c>
+      <c r="C64" s="0">
+        <v>1100</v>
+      </c>
+      <c r="D64" s="0">
+        <v>107</v>
+      </c>
+      <c r="E64" s="0" t="s">
+        <v>556</v>
+      </c>
+      <c r="F64" s="0" t="s">
+        <v>583</v>
+      </c>
+      <c r="G64" s="0" t="s">
+        <v>615</v>
+      </c>
+      <c r="H64" s="0">
+        <v>18748228</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="0" t="s">
+        <v>467</v>
+      </c>
+      <c r="B65" s="0" t="s">
+        <v>489</v>
+      </c>
+      <c r="C65" s="0">
+        <v>2100</v>
+      </c>
+      <c r="D65" s="0">
+        <v>107</v>
+      </c>
+      <c r="E65" s="0" t="s">
+        <v>557</v>
+      </c>
+      <c r="F65" s="0" t="s">
+        <v>583</v>
+      </c>
+      <c r="G65" s="0" t="s">
+        <v>615</v>
+      </c>
+      <c r="H65" s="0">
+        <v>18748229</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="0" t="s">
+        <v>467</v>
+      </c>
+      <c r="B66" s="0" t="s">
+        <v>507</v>
+      </c>
+      <c r="C66" s="0">
+        <v>1100</v>
+      </c>
+      <c r="D66" s="0">
+        <v>107</v>
+      </c>
+      <c r="E66" s="0" t="s">
+        <v>558</v>
+      </c>
+      <c r="F66" s="0" t="s">
+        <v>596</v>
+      </c>
+      <c r="G66" s="0" t="s">
+        <v>603</v>
+      </c>
+      <c r="H66" s="0">
+        <v>19623813</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="0" t="s">
+        <v>467</v>
+      </c>
+      <c r="B67" s="0" t="s">
+        <v>508</v>
+      </c>
+      <c r="C67" s="0">
+        <v>2100</v>
+      </c>
+      <c r="D67" s="0">
+        <v>107</v>
+      </c>
+      <c r="E67" s="0" t="s">
+        <v>559</v>
+      </c>
+      <c r="F67" s="0" t="s">
+        <v>596</v>
+      </c>
+      <c r="G67" s="0" t="s">
+        <v>603</v>
+      </c>
+      <c r="H67" s="0">
+        <v>19623814</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="0" t="s">
+        <v>468</v>
+      </c>
+      <c r="B68" s="0" t="s">
+        <v>277</v>
+      </c>
+      <c r="C68" s="0">
+        <v>1100</v>
+      </c>
+      <c r="D68" s="0">
+        <v>107</v>
+      </c>
+      <c r="E68" s="0" t="s">
+        <v>560</v>
+      </c>
+      <c r="F68" s="0" t="s">
+        <v>582</v>
+      </c>
+      <c r="G68" s="0" t="s">
+        <v>608</v>
+      </c>
+      <c r="H68" s="0">
+        <v>677164</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="0" t="s">
+        <v>468</v>
+      </c>
+      <c r="B69" s="0" t="s">
+        <v>278</v>
+      </c>
+      <c r="C69" s="0">
+        <v>2100</v>
+      </c>
+      <c r="D69" s="0">
+        <v>107</v>
+      </c>
+      <c r="E69" s="0" t="s">
+        <v>560</v>
+      </c>
+      <c r="F69" s="0" t="s">
+        <v>582</v>
+      </c>
+      <c r="G69" s="0" t="s">
+        <v>608</v>
+      </c>
+      <c r="H69" s="0">
+        <v>677112</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="0" t="s">
+        <v>468</v>
+      </c>
+      <c r="B70" s="0" t="s">
+        <v>509</v>
+      </c>
+      <c r="C70" s="0">
+        <v>2200</v>
+      </c>
+      <c r="D70" s="0">
+        <v>107</v>
+      </c>
+      <c r="E70" s="0"/>
+      <c r="F70" s="0" t="s">
+        <v>582</v>
+      </c>
+      <c r="G70" s="0" t="s">
+        <v>608</v>
+      </c>
+      <c r="H70" s="0">
+        <v>9271975</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="0" t="s">
+        <v>468</v>
+      </c>
+      <c r="B71" s="0" t="s">
+        <v>510</v>
+      </c>
+      <c r="C71" s="0">
+        <v>3400</v>
+      </c>
+      <c r="D71" s="0">
+        <v>107</v>
+      </c>
+      <c r="E71" s="0" t="s">
+        <v>561</v>
+      </c>
+      <c r="F71" s="0" t="s">
+        <v>597</v>
+      </c>
+      <c r="G71" s="0" t="s">
+        <v>625</v>
+      </c>
+      <c r="H71" s="0">
+        <v>19869294</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="0" t="s">
+        <v>469</v>
+      </c>
+      <c r="B72" s="0" t="s">
+        <v>277</v>
+      </c>
+      <c r="C72" s="0">
+        <v>1100</v>
+      </c>
+      <c r="D72" s="0">
+        <v>107</v>
+      </c>
+      <c r="E72" s="0" t="s">
+        <v>562</v>
+      </c>
+      <c r="F72" s="0" t="s">
+        <v>575</v>
+      </c>
+      <c r="G72" s="0" t="s">
+        <v>603</v>
+      </c>
+      <c r="H72" s="0">
+        <v>677142</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="0" t="s">
+        <v>469</v>
+      </c>
+      <c r="B73" s="0" t="s">
+        <v>278</v>
+      </c>
+      <c r="C73" s="0">
+        <v>2100</v>
+      </c>
+      <c r="D73" s="0">
+        <v>107</v>
+      </c>
+      <c r="E73" s="0" t="s">
+        <v>562</v>
+      </c>
+      <c r="F73" s="0" t="s">
+        <v>575</v>
+      </c>
+      <c r="G73" s="0" t="s">
+        <v>603</v>
+      </c>
+      <c r="H73" s="0">
+        <v>677167</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="0" t="s">
+        <v>470</v>
+      </c>
+      <c r="B74" s="0" t="s">
+        <v>277</v>
+      </c>
+      <c r="C74" s="0">
+        <v>1100</v>
+      </c>
+      <c r="D74" s="0">
+        <v>107</v>
+      </c>
+      <c r="E74" s="0" t="s">
+        <v>537</v>
+      </c>
+      <c r="F74" s="0" t="s">
+        <v>579</v>
+      </c>
+      <c r="G74" s="0" t="s">
+        <v>611</v>
+      </c>
+      <c r="H74" s="0">
+        <v>18905784</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="0" t="s">
+        <v>470</v>
+      </c>
+      <c r="B75" s="0" t="s">
+        <v>278</v>
+      </c>
+      <c r="C75" s="0">
+        <v>2100</v>
+      </c>
+      <c r="D75" s="0">
+        <v>107</v>
+      </c>
+      <c r="E75" s="0" t="s">
+        <v>537</v>
+      </c>
+      <c r="F75" s="0" t="s">
+        <v>579</v>
+      </c>
+      <c r="G75" s="0" t="s">
+        <v>611</v>
+      </c>
+      <c r="H75" s="0">
+        <v>18905783</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="0" t="s">
+        <v>471</v>
+      </c>
+      <c r="B76" s="0" t="s">
+        <v>277</v>
+      </c>
+      <c r="C76" s="0">
+        <v>1100</v>
+      </c>
+      <c r="D76" s="0">
+        <v>107</v>
+      </c>
+      <c r="E76" s="0" t="s">
+        <v>563</v>
+      </c>
+      <c r="F76" s="0" t="s">
+        <v>585</v>
+      </c>
+      <c r="G76" s="0" t="s">
+        <v>626</v>
+      </c>
+      <c r="H76" s="0">
+        <v>18866323</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="0" t="s">
+        <v>471</v>
+      </c>
+      <c r="B77" s="0" t="s">
+        <v>278</v>
+      </c>
+      <c r="C77" s="0">
+        <v>2100</v>
+      </c>
+      <c r="D77" s="0">
+        <v>107</v>
+      </c>
+      <c r="E77" s="0" t="s">
+        <v>564</v>
+      </c>
+      <c r="F77" s="0" t="s">
+        <v>585</v>
+      </c>
+      <c r="G77" s="0" t="s">
+        <v>626</v>
+      </c>
+      <c r="H77" s="0">
+        <v>18866324</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="0" t="s">
+        <v>472</v>
+      </c>
+      <c r="B78" s="0" t="s">
+        <v>511</v>
+      </c>
+      <c r="C78" s="0">
+        <v>3400</v>
+      </c>
+      <c r="D78" s="0">
+        <v>107</v>
+      </c>
+      <c r="E78" s="0" t="s">
+        <v>565</v>
+      </c>
+      <c r="F78" s="0" t="s">
+        <v>598</v>
+      </c>
+      <c r="G78" s="0" t="s">
+        <v>627</v>
+      </c>
+      <c r="H78" s="0">
+        <v>19032282</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="0" t="s">
+        <v>473</v>
+      </c>
+      <c r="B79" s="0" t="s">
+        <v>512</v>
+      </c>
+      <c r="C79" s="0">
+        <v>1100</v>
+      </c>
+      <c r="D79" s="0">
+        <v>107</v>
+      </c>
+      <c r="E79" s="0" t="s">
+        <v>566</v>
+      </c>
+      <c r="F79" s="0" t="s">
+        <v>599</v>
+      </c>
+      <c r="G79" s="0" t="s">
+        <v>609</v>
+      </c>
+      <c r="H79" s="0">
+        <v>6737411</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="0" t="s">
+        <v>473</v>
+      </c>
+      <c r="B80" s="0" t="s">
+        <v>513</v>
+      </c>
+      <c r="C80" s="0">
+        <v>2100</v>
+      </c>
+      <c r="D80" s="0">
+        <v>107</v>
+      </c>
+      <c r="E80" s="0" t="s">
+        <v>566</v>
+      </c>
+      <c r="F80" s="0" t="s">
+        <v>599</v>
+      </c>
+      <c r="G80" s="0" t="s">
+        <v>609</v>
+      </c>
+      <c r="H80" s="0">
+        <v>6737412</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="0" t="s">
+        <v>473</v>
+      </c>
+      <c r="B81" s="0" t="s">
+        <v>514</v>
+      </c>
+      <c r="C81" s="0">
+        <v>1100</v>
+      </c>
+      <c r="D81" s="0">
+        <v>107</v>
+      </c>
+      <c r="E81" s="0" t="s">
+        <v>566</v>
+      </c>
+      <c r="F81" s="0" t="s">
+        <v>600</v>
+      </c>
+      <c r="G81" s="0" t="s">
+        <v>609</v>
+      </c>
+      <c r="H81" s="0">
+        <v>6737413</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="0" t="s">
+        <v>473</v>
+      </c>
+      <c r="B82" s="0" t="s">
+        <v>515</v>
+      </c>
+      <c r="C82" s="0">
+        <v>2100</v>
+      </c>
+      <c r="D82" s="0">
+        <v>107</v>
+      </c>
+      <c r="E82" s="0" t="s">
+        <v>566</v>
+      </c>
+      <c r="F82" s="0" t="s">
+        <v>600</v>
+      </c>
+      <c r="G82" s="0" t="s">
+        <v>609</v>
+      </c>
+      <c r="H82" s="0">
+        <v>6737414</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="0" t="s">
+        <v>474</v>
+      </c>
+      <c r="B83" s="0" t="s">
+        <v>277</v>
+      </c>
+      <c r="C83" s="0">
+        <v>1100</v>
+      </c>
+      <c r="D83" s="0">
+        <v>107</v>
+      </c>
+      <c r="E83" s="0" t="s">
+        <v>567</v>
+      </c>
+      <c r="F83" s="0" t="s">
+        <v>601</v>
+      </c>
+      <c r="G83" s="0" t="s">
+        <v>612</v>
+      </c>
+      <c r="H83" s="0">
+        <v>18771406</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="0" t="s">
+        <v>474</v>
+      </c>
+      <c r="B84" s="0" t="s">
+        <v>278</v>
+      </c>
+      <c r="C84" s="0">
+        <v>2100</v>
+      </c>
+      <c r="D84" s="0">
+        <v>107</v>
+      </c>
+      <c r="E84" s="0" t="s">
+        <v>567</v>
+      </c>
+      <c r="F84" s="0" t="s">
+        <v>601</v>
+      </c>
+      <c r="G84" s="0" t="s">
+        <v>612</v>
+      </c>
+      <c r="H84" s="0">
+        <v>18771407</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="0" t="s">
+        <v>475</v>
+      </c>
+      <c r="B85" s="0" t="s">
+        <v>277</v>
+      </c>
+      <c r="C85" s="0">
+        <v>1100</v>
+      </c>
+      <c r="D85" s="0">
+        <v>107</v>
+      </c>
+      <c r="E85" s="0" t="s">
+        <v>568</v>
+      </c>
+      <c r="F85" s="0" t="s">
+        <v>602</v>
+      </c>
+      <c r="G85" s="0" t="s">
+        <v>606</v>
+      </c>
+      <c r="H85" s="0">
+        <v>19479016</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="0" t="s">
+        <v>475</v>
+      </c>
+      <c r="B86" s="0" t="s">
+        <v>278</v>
+      </c>
+      <c r="C86" s="0">
+        <v>2100</v>
+      </c>
+      <c r="D86" s="0">
+        <v>107</v>
+      </c>
+      <c r="E86" s="0" t="s">
+        <v>568</v>
+      </c>
+      <c r="F86" s="0" t="s">
+        <v>602</v>
+      </c>
+      <c r="G86" s="0" t="s">
+        <v>606</v>
+      </c>
+      <c r="H86" s="0">
+        <v>19479015</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="0" t="s">
+        <v>476</v>
+      </c>
+      <c r="B87" s="0" t="s">
+        <v>277</v>
+      </c>
+      <c r="C87" s="0">
+        <v>1100</v>
+      </c>
+      <c r="D87" s="0">
+        <v>107</v>
+      </c>
+      <c r="E87" s="0" t="s">
+        <v>569</v>
+      </c>
+      <c r="F87" s="0" t="s">
+        <v>579</v>
+      </c>
+      <c r="G87" s="0" t="s">
+        <v>611</v>
+      </c>
+      <c r="H87" s="0">
+        <v>18905786</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="0" t="s">
+        <v>476</v>
+      </c>
+      <c r="B88" s="0" t="s">
+        <v>278</v>
+      </c>
+      <c r="C88" s="0">
+        <v>2100</v>
+      </c>
+      <c r="D88" s="0">
+        <v>107</v>
+      </c>
+      <c r="E88" s="0" t="s">
+        <v>569</v>
+      </c>
+      <c r="F88" s="0" t="s">
+        <v>579</v>
+      </c>
+      <c r="G88" s="0" t="s">
+        <v>611</v>
+      </c>
+      <c r="H88" s="0">
+        <v>18905785</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D7"/>

--- a/Region_data_UD.xlsx
+++ b/Region_data_UD.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1303" uniqueCount="628">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1590" uniqueCount="838">
   <si>
     <t>Name</t>
   </si>
@@ -1330,6 +1330,390 @@
     <t>Gary Henderson</t>
   </si>
   <si>
+    <t>Richard weir</t>
+  </si>
+  <si>
+    <t>Andrew Fox</t>
+  </si>
+  <si>
+    <t>Alan Hutchison</t>
+  </si>
+  <si>
+    <t>scott Tipping</t>
+  </si>
+  <si>
+    <t>James McKendry</t>
+  </si>
+  <si>
+    <t>Joseph McIvor</t>
+  </si>
+  <si>
+    <t>Keith Cassidy</t>
+  </si>
+  <si>
+    <t>Rachael Allison</t>
+  </si>
+  <si>
+    <t>Graham McCallum</t>
+  </si>
+  <si>
+    <t>Alan Clark</t>
+  </si>
+  <si>
+    <t>Paul Murphy</t>
+  </si>
+  <si>
+    <t>Steven Sutherland</t>
+  </si>
+  <si>
+    <t>Steven Taylor</t>
+  </si>
+  <si>
+    <t>Andrew Wardlaw</t>
+  </si>
+  <si>
+    <t>Steven Thomson</t>
+  </si>
+  <si>
+    <t>Kelvin John</t>
+  </si>
+  <si>
+    <t>James Brown</t>
+  </si>
+  <si>
+    <t>Pawel Reuter</t>
+  </si>
+  <si>
+    <t>Kierin Slavin</t>
+  </si>
+  <si>
+    <t>Robert Whyte</t>
+  </si>
+  <si>
+    <t>Sean O'Leary</t>
+  </si>
+  <si>
+    <t>scott Gray</t>
+  </si>
+  <si>
+    <t>Naomi Watson</t>
+  </si>
+  <si>
+    <t>Nicole Smith</t>
+  </si>
+  <si>
+    <t>Cameron Brown</t>
+  </si>
+  <si>
+    <t>Peter McCulloch</t>
+  </si>
+  <si>
+    <t>James Mitchell</t>
+  </si>
+  <si>
+    <t>Philip McRory</t>
+  </si>
+  <si>
+    <t>Christopher O'Donnell</t>
+  </si>
+  <si>
+    <t>IAIN Gray</t>
+  </si>
+  <si>
+    <t>Ross Morgan</t>
+  </si>
+  <si>
+    <t>Thomas Shaw</t>
+  </si>
+  <si>
+    <t>Owen Rankin</t>
+  </si>
+  <si>
+    <t>Dylan Yardley</t>
+  </si>
+  <si>
+    <t>Ervis Krasniqi</t>
+  </si>
+  <si>
+    <t>Stuart AITKEN</t>
+  </si>
+  <si>
+    <t>Matthew Fleming</t>
+  </si>
+  <si>
+    <t>Sam Baillie</t>
+  </si>
+  <si>
+    <t>Adam Smith</t>
+  </si>
+  <si>
+    <t>Gavin Hamilton</t>
+  </si>
+  <si>
+    <t>kieran McDonald</t>
+  </si>
+  <si>
+    <t>Dougal Browne</t>
+  </si>
+  <si>
+    <t>Edgar Chidavaenzi</t>
+  </si>
+  <si>
+    <t>Robert Turner</t>
+  </si>
+  <si>
+    <t>David Mungall</t>
+  </si>
+  <si>
+    <t>Grant MacKay</t>
+  </si>
+  <si>
+    <t>James Mccall</t>
+  </si>
+  <si>
+    <t>Christopher Johnston</t>
+  </si>
+  <si>
+    <t>Corrie Beattie</t>
+  </si>
+  <si>
+    <t>Ian Addison</t>
+  </si>
+  <si>
+    <t>Alasdair Campbell</t>
+  </si>
+  <si>
+    <t>Greig Sharpe</t>
+  </si>
+  <si>
+    <t>kieran Georgallis</t>
+  </si>
+  <si>
+    <t>Dominic Black</t>
+  </si>
+  <si>
+    <t>Ben Mcilvaney</t>
+  </si>
+  <si>
+    <t>Owen Mitchell</t>
+  </si>
+  <si>
+    <t>aiden Mcgregor</t>
+  </si>
+  <si>
+    <t>Susan McAuslan</t>
+  </si>
+  <si>
+    <t>Derek Walker</t>
+  </si>
+  <si>
+    <t>Kenneth Lindsay</t>
+  </si>
+  <si>
+    <t>Andrew Mulligan</t>
+  </si>
+  <si>
+    <t>Callum Fullelove</t>
+  </si>
+  <si>
+    <t>Daniel Hall</t>
+  </si>
+  <si>
+    <t>Mark bowrman</t>
+  </si>
+  <si>
+    <t>Alan Campbell</t>
+  </si>
+  <si>
+    <t>John Kane</t>
+  </si>
+  <si>
+    <t>Harry Gibbons</t>
+  </si>
+  <si>
+    <t>David Rose</t>
+  </si>
+  <si>
+    <t>Bradley Fulton</t>
+  </si>
+  <si>
+    <t>Darren Jude</t>
+  </si>
+  <si>
+    <t>John Sutherland</t>
+  </si>
+  <si>
+    <t>Lee Morrison</t>
+  </si>
+  <si>
+    <t>Jonathan Ramp</t>
+  </si>
+  <si>
+    <t>Ziad Afzal</t>
+  </si>
+  <si>
+    <t>Evan Kerr</t>
+  </si>
+  <si>
+    <t>Flynn Mimnaugh</t>
+  </si>
+  <si>
+    <t>Ross Mitchell</t>
+  </si>
+  <si>
+    <t>Cameron Mason</t>
+  </si>
+  <si>
+    <t>Abbie Connolly</t>
+  </si>
+  <si>
+    <t>kieran Laing</t>
+  </si>
+  <si>
+    <t>Mark McLaughlin</t>
+  </si>
+  <si>
+    <t>Ross Macmillan</t>
+  </si>
+  <si>
+    <t>scott MacDonald</t>
+  </si>
+  <si>
+    <t>Christopher Cleghorne</t>
+  </si>
+  <si>
+    <t>Alistair Orr</t>
+  </si>
+  <si>
+    <t>scott IRVING</t>
+  </si>
+  <si>
+    <t>Andrew Milligan</t>
+  </si>
+  <si>
+    <t>William Mcgettigan</t>
+  </si>
+  <si>
+    <t>kieran Neal</t>
+  </si>
+  <si>
+    <t>David Peacock</t>
+  </si>
+  <si>
+    <t>Colin Hamilton</t>
+  </si>
+  <si>
+    <t>Mark wallace</t>
+  </si>
+  <si>
+    <t>Shane Murphy</t>
+  </si>
+  <si>
+    <t>Barrie Anderson</t>
+  </si>
+  <si>
+    <t>Bryan Dingwall</t>
+  </si>
+  <si>
+    <t>IAIN Neil</t>
+  </si>
+  <si>
+    <t>Gavin Lindsay</t>
+  </si>
+  <si>
+    <t>Graham Warnock</t>
+  </si>
+  <si>
+    <t>James Forrest</t>
+  </si>
+  <si>
+    <t>Thomas Cordery</t>
+  </si>
+  <si>
+    <t>James Barrie</t>
+  </si>
+  <si>
+    <t>Gary MacCuish</t>
+  </si>
+  <si>
+    <t>Colin Perry</t>
+  </si>
+  <si>
+    <t>Alexander Smith</t>
+  </si>
+  <si>
+    <t>Gary Tyczynski</t>
+  </si>
+  <si>
+    <t>Kevin Petto</t>
+  </si>
+  <si>
+    <t>Thomas McCulloch</t>
+  </si>
+  <si>
+    <t>Steven Toner</t>
+  </si>
+  <si>
+    <t>Lachlan Farries</t>
+  </si>
+  <si>
+    <t>David Irvine</t>
+  </si>
+  <si>
+    <t>Mark Thallon</t>
+  </si>
+  <si>
+    <t>Gary Scott</t>
+  </si>
+  <si>
+    <t>Edward Hughes</t>
+  </si>
+  <si>
+    <t>Gordon Sackey</t>
+  </si>
+  <si>
+    <t>John Mcnulty</t>
+  </si>
+  <si>
+    <t>Peter Hamilton</t>
+  </si>
+  <si>
+    <t>Alan greenshields</t>
+  </si>
+  <si>
+    <t>Grant Macvarish</t>
+  </si>
+  <si>
+    <t>Richard Lyon</t>
+  </si>
+  <si>
+    <t>Douglas Campbell</t>
+  </si>
+  <si>
+    <t>Calum mcintosh</t>
+  </si>
+  <si>
+    <t>Kevin Stirrat</t>
+  </si>
+  <si>
+    <t>James Thomson</t>
+  </si>
+  <si>
+    <t>Ross Kennedy</t>
+  </si>
+  <si>
+    <t>David Gray</t>
+  </si>
+  <si>
+    <t>Peter Gordon</t>
+  </si>
+  <si>
+    <t>Gary Moreland</t>
+  </si>
+  <si>
+    <t>Craig Martin</t>
+  </si>
+  <si>
     <t>aa</t>
   </si>
   <si>
@@ -1360,6 +1744,234 @@
     <t>gh</t>
   </si>
   <si>
+    <t>rw</t>
+  </si>
+  <si>
+    <t>af</t>
+  </si>
+  <si>
+    <t>ah</t>
+  </si>
+  <si>
+    <t>st</t>
+  </si>
+  <si>
+    <t>jm</t>
+  </si>
+  <si>
+    <t>kc</t>
+  </si>
+  <si>
+    <t>ra</t>
+  </si>
+  <si>
+    <t>ac</t>
+  </si>
+  <si>
+    <t>pm</t>
+  </si>
+  <si>
+    <t>ss</t>
+  </si>
+  <si>
+    <t>aw</t>
+  </si>
+  <si>
+    <t>kj</t>
+  </si>
+  <si>
+    <t>jb</t>
+  </si>
+  <si>
+    <t>pr</t>
+  </si>
+  <si>
+    <t>sg</t>
+  </si>
+  <si>
+    <t>nw</t>
+  </si>
+  <si>
+    <t>ns</t>
+  </si>
+  <si>
+    <t>co</t>
+  </si>
+  <si>
+    <t>ig</t>
+  </si>
+  <si>
+    <t>rm</t>
+  </si>
+  <si>
+    <t>or</t>
+  </si>
+  <si>
+    <t>dy</t>
+  </si>
+  <si>
+    <t>ek</t>
+  </si>
+  <si>
+    <t>sa</t>
+  </si>
+  <si>
+    <t>km</t>
+  </si>
+  <si>
+    <t>ec</t>
+  </si>
+  <si>
+    <t>rt</t>
+  </si>
+  <si>
+    <t>cj</t>
+  </si>
+  <si>
+    <t>ia</t>
+  </si>
+  <si>
+    <t>gs</t>
+  </si>
+  <si>
+    <t>kg</t>
+  </si>
+  <si>
+    <t>bm</t>
+  </si>
+  <si>
+    <t>om</t>
+  </si>
+  <si>
+    <t>am</t>
+  </si>
+  <si>
+    <t>dw</t>
+  </si>
+  <si>
+    <t>kl</t>
+  </si>
+  <si>
+    <t>cf</t>
+  </si>
+  <si>
+    <t>dh</t>
+  </si>
+  <si>
+    <t>jk</t>
+  </si>
+  <si>
+    <t>hg</t>
+  </si>
+  <si>
+    <t>dr</t>
+  </si>
+  <si>
+    <t>bf</t>
+  </si>
+  <si>
+    <t>js</t>
+  </si>
+  <si>
+    <t>lm</t>
+  </si>
+  <si>
+    <t>jr</t>
+  </si>
+  <si>
+    <t>za</t>
+  </si>
+  <si>
+    <t>fm</t>
+  </si>
+  <si>
+    <t>cm</t>
+  </si>
+  <si>
+    <t>mm</t>
+  </si>
+  <si>
+    <t>cc</t>
+  </si>
+  <si>
+    <t>ao</t>
+  </si>
+  <si>
+    <t>si</t>
+  </si>
+  <si>
+    <t>wm</t>
+  </si>
+  <si>
+    <t>kn</t>
+  </si>
+  <si>
+    <t>ch</t>
+  </si>
+  <si>
+    <t>mw</t>
+  </si>
+  <si>
+    <t>bd</t>
+  </si>
+  <si>
+    <t>in</t>
+  </si>
+  <si>
+    <t>gl</t>
+  </si>
+  <si>
+    <t>gw</t>
+  </si>
+  <si>
+    <t>jf</t>
+  </si>
+  <si>
+    <t>tc</t>
+  </si>
+  <si>
+    <t>cp</t>
+  </si>
+  <si>
+    <t>gt</t>
+  </si>
+  <si>
+    <t>kp</t>
+  </si>
+  <si>
+    <t>tm</t>
+  </si>
+  <si>
+    <t>lf</t>
+  </si>
+  <si>
+    <t>di</t>
+  </si>
+  <si>
+    <t>mt</t>
+  </si>
+  <si>
+    <t>eh</t>
+  </si>
+  <si>
+    <t>ph</t>
+  </si>
+  <si>
+    <t>dc</t>
+  </si>
+  <si>
+    <t>jt</t>
+  </si>
+  <si>
+    <t>rk</t>
+  </si>
+  <si>
+    <t>dg</t>
+  </si>
+  <si>
+    <t>pg</t>
+  </si>
+  <si>
     <t>Bathgate Fs</t>
   </si>
   <si>
@@ -1423,6 +2035,9 @@
     <t>Midcalder Junction</t>
   </si>
   <si>
+    <t>Monktonhall</t>
+  </si>
+  <si>
     <t>Muirhouse Jn</t>
   </si>
   <si>
@@ -1447,6 +2062,9 @@
     <t>Polmont Junction</t>
   </si>
   <si>
+    <t>Portobello</t>
+  </si>
+  <si>
     <t>Rutherglen</t>
   </si>
   <si>
@@ -1516,6 +2134,18 @@
     <t>Down Main(Ghl)</t>
   </si>
   <si>
+    <t>Up South</t>
+  </si>
+  <si>
+    <t>Down South</t>
+  </si>
+  <si>
+    <t>Up North</t>
+  </si>
+  <si>
+    <t>Down North</t>
+  </si>
+  <si>
     <t>Up Main (Wwd)</t>
   </si>
   <si>
@@ -1645,10 +2275,7 @@
     <t>GD/32/34</t>
   </si>
   <si>
-    <t>PC2K</t>
-  </si>
-  <si>
-    <t>CH5B</t>
+    <t>E/636/08</t>
   </si>
   <si>
     <t>GL/4/04</t>
@@ -1657,10 +2284,7 @@
     <t>GL/3/04</t>
   </si>
   <si>
-    <t>GL5/03</t>
-  </si>
-  <si>
-    <t>GL6/5F</t>
+    <t>GM/08/04A</t>
   </si>
   <si>
     <t>ES/01/20</t>
@@ -1678,10 +2302,10 @@
     <t>GG/00/08</t>
   </si>
   <si>
-    <t>GL7/04</t>
-  </si>
-  <si>
-    <t>GL7/05</t>
+    <t>GT/34/24</t>
+  </si>
+  <si>
+    <t>EW/00/20A</t>
   </si>
   <si>
     <t>K/00/20</t>
@@ -1699,16 +2323,10 @@
     <t>E626/22A</t>
   </si>
   <si>
-    <t>RN3G</t>
-  </si>
-  <si>
-    <t>RN4A</t>
-  </si>
-  <si>
-    <t>BH3</t>
-  </si>
-  <si>
-    <t>CH6G/BH4</t>
+    <t>EG/61/16</t>
+  </si>
+  <si>
+    <t>F/50/03</t>
   </si>
   <si>
     <t>G/636/17</t>
@@ -1726,6 +2344,9 @@
     <t>EP/00/21</t>
   </si>
   <si>
+    <t>E/626/22A</t>
+  </si>
+  <si>
     <t>RW/0/16</t>
   </si>
   <si>
@@ -1792,6 +2413,9 @@
     <t>EGM2</t>
   </si>
   <si>
+    <t>ECN2</t>
+  </si>
+  <si>
     <t>WWD</t>
   </si>
   <si>
@@ -1810,6 +2434,9 @@
     <t>RCB</t>
   </si>
   <si>
+    <t>MHL2</t>
+  </si>
+  <si>
     <t>MEN2</t>
   </si>
   <si>
@@ -1895,6 +2522,9 @@
   </si>
   <si>
     <t>GG</t>
+  </si>
+  <si>
+    <t>EW</t>
   </si>
   <si>
     <t>EK</t>
@@ -4086,13 +4716,13 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D140"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16.5703125" customWidth="true"/>
+    <col min="1" max="1" width="21.140625" customWidth="true"/>
     <col min="2" max="2" width="8.42578125" customWidth="true"/>
     <col min="3" max="3" width="5.85546875" customWidth="true"/>
-    <col min="4" max="4" width="4.140625" customWidth="true"/>
+    <col min="4" max="4" width="4.5703125" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4120,7 +4750,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>433</v>
+        <v>561</v>
       </c>
     </row>
     <row r="3">
@@ -4134,7 +4764,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>434</v>
+        <v>562</v>
       </c>
     </row>
     <row r="4">
@@ -4148,7 +4778,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>435</v>
+        <v>563</v>
       </c>
     </row>
     <row r="5">
@@ -4162,7 +4792,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>436</v>
+        <v>564</v>
       </c>
     </row>
     <row r="6">
@@ -4176,7 +4806,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>437</v>
+        <v>565</v>
       </c>
     </row>
     <row r="7">
@@ -4190,7 +4820,7 @@
         <v>1</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>438</v>
+        <v>566</v>
       </c>
     </row>
     <row r="8">
@@ -4218,7 +4848,7 @@
         <v>1</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>439</v>
+        <v>567</v>
       </c>
     </row>
     <row r="10">
@@ -4232,7 +4862,7 @@
         <v>1</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>440</v>
+        <v>568</v>
       </c>
     </row>
     <row r="11">
@@ -4246,7 +4876,7 @@
         <v>1</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>441</v>
+        <v>569</v>
       </c>
     </row>
     <row r="12">
@@ -4260,7 +4890,1799 @@
         <v>1</v>
       </c>
       <c r="D12" s="0" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="s">
+        <v>433</v>
+      </c>
+      <c r="B13" s="0">
+        <v>1073052</v>
+      </c>
+      <c r="C13" s="0">
+        <v>1</v>
+      </c>
+      <c r="D13" s="0" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="s">
+        <v>434</v>
+      </c>
+      <c r="B14" s="0">
+        <v>1073986</v>
+      </c>
+      <c r="C14" s="0">
+        <v>1</v>
+      </c>
+      <c r="D14" s="0" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="s">
+        <v>435</v>
+      </c>
+      <c r="B15" s="0">
+        <v>1074109</v>
+      </c>
+      <c r="C15" s="0">
+        <v>1</v>
+      </c>
+      <c r="D15" s="0" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0" t="s">
+        <v>436</v>
+      </c>
+      <c r="B16" s="0">
+        <v>1074112</v>
+      </c>
+      <c r="C16" s="0">
+        <v>1</v>
+      </c>
+      <c r="D16" s="0" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0" t="s">
+        <v>437</v>
+      </c>
+      <c r="B17" s="0">
+        <v>686619</v>
+      </c>
+      <c r="C17" s="0">
+        <v>1</v>
+      </c>
+      <c r="D17" s="0" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="0" t="s">
+        <v>438</v>
+      </c>
+      <c r="B18" s="0">
+        <v>1074108</v>
+      </c>
+      <c r="C18" s="0">
+        <v>1</v>
+      </c>
+      <c r="D18" s="0" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="0" t="s">
+        <v>439</v>
+      </c>
+      <c r="B19" s="0">
+        <v>1073353</v>
+      </c>
+      <c r="C19" s="0">
+        <v>1</v>
+      </c>
+      <c r="D19" s="0" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="0" t="s">
+        <v>440</v>
+      </c>
+      <c r="B20" s="0">
+        <v>1087053</v>
+      </c>
+      <c r="C20" s="0">
+        <v>1</v>
+      </c>
+      <c r="D20" s="0" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="s">
+        <v>441</v>
+      </c>
+      <c r="B21" s="0">
+        <v>1087868</v>
+      </c>
+      <c r="C21" s="0">
+        <v>1</v>
+      </c>
+      <c r="D21" s="0" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="0" t="s">
         <v>442</v>
+      </c>
+      <c r="B22" s="0">
+        <v>1035592</v>
+      </c>
+      <c r="C22" s="0">
+        <v>1</v>
+      </c>
+      <c r="D22" s="0" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="0" t="s">
+        <v>443</v>
+      </c>
+      <c r="B23" s="0">
+        <v>1112638</v>
+      </c>
+      <c r="C23" s="0">
+        <v>1</v>
+      </c>
+      <c r="D23" s="0" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="0" t="s">
+        <v>444</v>
+      </c>
+      <c r="B24" s="0">
+        <v>1012174</v>
+      </c>
+      <c r="C24" s="0">
+        <v>1</v>
+      </c>
+      <c r="D24" s="0" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0" t="s">
+        <v>445</v>
+      </c>
+      <c r="B25" s="0">
+        <v>1164878</v>
+      </c>
+      <c r="C25" s="0">
+        <v>1</v>
+      </c>
+      <c r="D25" s="0" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="s">
+        <v>446</v>
+      </c>
+      <c r="B26" s="0">
+        <v>1164885</v>
+      </c>
+      <c r="C26" s="0">
+        <v>1</v>
+      </c>
+      <c r="D26" s="0" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="s">
+        <v>447</v>
+      </c>
+      <c r="B27" s="0">
+        <v>1135230</v>
+      </c>
+      <c r="C27" s="0">
+        <v>1</v>
+      </c>
+      <c r="D27" s="0" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="s">
+        <v>448</v>
+      </c>
+      <c r="B28" s="0">
+        <v>1052263</v>
+      </c>
+      <c r="C28" s="0">
+        <v>1</v>
+      </c>
+      <c r="D28" s="0" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="s">
+        <v>449</v>
+      </c>
+      <c r="B29" s="0">
+        <v>1035596</v>
+      </c>
+      <c r="C29" s="0">
+        <v>1</v>
+      </c>
+      <c r="D29" s="0" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="0" t="s">
+        <v>450</v>
+      </c>
+      <c r="B30" s="0">
+        <v>1213270</v>
+      </c>
+      <c r="C30" s="0">
+        <v>1</v>
+      </c>
+      <c r="D30" s="0" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="0" t="s">
+        <v>451</v>
+      </c>
+      <c r="B31" s="0">
+        <v>1214877</v>
+      </c>
+      <c r="C31" s="0">
+        <v>1</v>
+      </c>
+      <c r="D31" s="0" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="0" t="s">
+        <v>452</v>
+      </c>
+      <c r="B32" s="0">
+        <v>661680</v>
+      </c>
+      <c r="C32" s="0">
+        <v>1</v>
+      </c>
+      <c r="D32" s="0" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="0" t="s">
+        <v>453</v>
+      </c>
+      <c r="B33" s="0">
+        <v>1215757</v>
+      </c>
+      <c r="C33" s="0">
+        <v>1</v>
+      </c>
+      <c r="D33" s="0" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="0" t="s">
+        <v>454</v>
+      </c>
+      <c r="B34" s="0">
+        <v>1097290</v>
+      </c>
+      <c r="C34" s="0">
+        <v>1</v>
+      </c>
+      <c r="D34" s="0" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="0" t="s">
+        <v>455</v>
+      </c>
+      <c r="B35" s="0">
+        <v>1237456</v>
+      </c>
+      <c r="C35" s="0">
+        <v>1</v>
+      </c>
+      <c r="D35" s="0" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="0" t="s">
+        <v>456</v>
+      </c>
+      <c r="B36" s="0">
+        <v>1237573</v>
+      </c>
+      <c r="C36" s="0">
+        <v>1</v>
+      </c>
+      <c r="D36" s="0" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="0" t="s">
+        <v>457</v>
+      </c>
+      <c r="B37" s="0">
+        <v>1237455</v>
+      </c>
+      <c r="C37" s="0">
+        <v>1</v>
+      </c>
+      <c r="D37" s="0" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="0" t="s">
+        <v>458</v>
+      </c>
+      <c r="B38" s="0">
+        <v>1238312</v>
+      </c>
+      <c r="C38" s="0">
+        <v>1</v>
+      </c>
+      <c r="D38" s="0" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="0" t="s">
+        <v>459</v>
+      </c>
+      <c r="B39" s="0">
+        <v>1242685</v>
+      </c>
+      <c r="C39" s="0">
+        <v>1</v>
+      </c>
+      <c r="D39" s="0" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="0" t="s">
+        <v>460</v>
+      </c>
+      <c r="B40" s="0">
+        <v>1198276</v>
+      </c>
+      <c r="C40" s="0">
+        <v>1</v>
+      </c>
+      <c r="D40" s="0" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="0" t="s">
+        <v>461</v>
+      </c>
+      <c r="B41" s="0">
+        <v>1220732</v>
+      </c>
+      <c r="C41" s="0">
+        <v>1</v>
+      </c>
+      <c r="D41" s="0" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="0" t="s">
+        <v>462</v>
+      </c>
+      <c r="B42" s="0">
+        <v>1172264</v>
+      </c>
+      <c r="C42" s="0">
+        <v>1</v>
+      </c>
+      <c r="D42" s="0" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="0" t="s">
+        <v>463</v>
+      </c>
+      <c r="B43" s="0">
+        <v>1247892</v>
+      </c>
+      <c r="C43" s="0">
+        <v>1</v>
+      </c>
+      <c r="D43" s="0" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="0" t="s">
+        <v>464</v>
+      </c>
+      <c r="B44" s="0">
+        <v>1247889</v>
+      </c>
+      <c r="C44" s="0">
+        <v>1</v>
+      </c>
+      <c r="D44" s="0" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="0" t="s">
+        <v>465</v>
+      </c>
+      <c r="B45" s="0">
+        <v>1124072</v>
+      </c>
+      <c r="C45" s="0">
+        <v>1</v>
+      </c>
+      <c r="D45" s="0" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="0" t="s">
+        <v>466</v>
+      </c>
+      <c r="B46" s="0">
+        <v>1250852</v>
+      </c>
+      <c r="C46" s="0">
+        <v>1</v>
+      </c>
+      <c r="D46" s="0" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="0" t="s">
+        <v>467</v>
+      </c>
+      <c r="B47" s="0">
+        <v>1061946</v>
+      </c>
+      <c r="C47" s="0">
+        <v>1</v>
+      </c>
+      <c r="D47" s="0" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="0" t="s">
+        <v>468</v>
+      </c>
+      <c r="B48" s="0">
+        <v>1089577</v>
+      </c>
+      <c r="C48" s="0">
+        <v>1</v>
+      </c>
+      <c r="D48" s="0" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="0" t="s">
+        <v>469</v>
+      </c>
+      <c r="B49" s="0">
+        <v>1116513</v>
+      </c>
+      <c r="C49" s="0">
+        <v>1</v>
+      </c>
+      <c r="D49" s="0" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="0" t="s">
+        <v>470</v>
+      </c>
+      <c r="B50" s="0">
+        <v>1217492</v>
+      </c>
+      <c r="C50" s="0">
+        <v>1</v>
+      </c>
+      <c r="D50" s="0" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="0" t="s">
+        <v>471</v>
+      </c>
+      <c r="B51" s="0">
+        <v>1179742</v>
+      </c>
+      <c r="C51" s="0">
+        <v>1</v>
+      </c>
+      <c r="D51" s="0" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="0" t="s">
+        <v>472</v>
+      </c>
+      <c r="B52" s="0">
+        <v>1200181</v>
+      </c>
+      <c r="C52" s="0">
+        <v>1</v>
+      </c>
+      <c r="D52" s="0" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="0" t="s">
+        <v>473</v>
+      </c>
+      <c r="B53" s="0">
+        <v>1189118</v>
+      </c>
+      <c r="C53" s="0">
+        <v>1</v>
+      </c>
+      <c r="D53" s="0" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="0" t="s">
+        <v>474</v>
+      </c>
+      <c r="B54" s="0">
+        <v>1267319</v>
+      </c>
+      <c r="C54" s="0">
+        <v>1</v>
+      </c>
+      <c r="D54" s="0" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="0" t="s">
+        <v>475</v>
+      </c>
+      <c r="B55" s="0">
+        <v>1270007</v>
+      </c>
+      <c r="C55" s="0">
+        <v>1</v>
+      </c>
+      <c r="D55" s="0" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="0" t="s">
+        <v>476</v>
+      </c>
+      <c r="B56" s="0">
+        <v>1224070</v>
+      </c>
+      <c r="C56" s="0">
+        <v>1</v>
+      </c>
+      <c r="D56" s="0" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="0" t="s">
+        <v>477</v>
+      </c>
+      <c r="B57" s="0">
+        <v>683316</v>
+      </c>
+      <c r="C57" s="0">
+        <v>1</v>
+      </c>
+      <c r="D57" s="0" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="0" t="s">
+        <v>478</v>
+      </c>
+      <c r="B58" s="0">
+        <v>678615</v>
+      </c>
+      <c r="C58" s="0">
+        <v>1</v>
+      </c>
+      <c r="D58" s="0" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="0" t="s">
+        <v>479</v>
+      </c>
+      <c r="B59" s="0">
+        <v>1284995</v>
+      </c>
+      <c r="C59" s="0">
+        <v>1</v>
+      </c>
+      <c r="D59" s="0" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="0" t="s">
+        <v>480</v>
+      </c>
+      <c r="B60" s="0">
+        <v>1120800</v>
+      </c>
+      <c r="C60" s="0">
+        <v>1</v>
+      </c>
+      <c r="D60" s="0" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="0" t="s">
+        <v>481</v>
+      </c>
+      <c r="B61" s="0">
+        <v>1296457</v>
+      </c>
+      <c r="C61" s="0">
+        <v>1</v>
+      </c>
+      <c r="D61" s="0" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="0" t="s">
+        <v>482</v>
+      </c>
+      <c r="B62" s="0">
+        <v>1302656</v>
+      </c>
+      <c r="C62" s="0">
+        <v>1</v>
+      </c>
+      <c r="D62" s="0" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="0" t="s">
+        <v>483</v>
+      </c>
+      <c r="B63" s="0">
+        <v>1302653</v>
+      </c>
+      <c r="C63" s="0">
+        <v>1</v>
+      </c>
+      <c r="D63" s="0" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="0" t="s">
+        <v>484</v>
+      </c>
+      <c r="B64" s="0">
+        <v>1114036</v>
+      </c>
+      <c r="C64" s="0">
+        <v>1</v>
+      </c>
+      <c r="D64" s="0" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="0" t="s">
+        <v>485</v>
+      </c>
+      <c r="B65" s="0">
+        <v>694275</v>
+      </c>
+      <c r="C65" s="0">
+        <v>1</v>
+      </c>
+      <c r="D65" s="0" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="0" t="s">
+        <v>486</v>
+      </c>
+      <c r="B66" s="0">
+        <v>431218</v>
+      </c>
+      <c r="C66" s="0">
+        <v>1</v>
+      </c>
+      <c r="D66" s="0" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="0" t="s">
+        <v>487</v>
+      </c>
+      <c r="B67" s="0">
+        <v>1269781</v>
+      </c>
+      <c r="C67" s="0">
+        <v>1</v>
+      </c>
+      <c r="D67" s="0" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="0" t="s">
+        <v>488</v>
+      </c>
+      <c r="B68" s="0">
+        <v>1338404</v>
+      </c>
+      <c r="C68" s="0">
+        <v>1</v>
+      </c>
+      <c r="D68" s="0" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="0" t="s">
+        <v>489</v>
+      </c>
+      <c r="B69" s="0">
+        <v>1337860</v>
+      </c>
+      <c r="C69" s="0">
+        <v>1</v>
+      </c>
+      <c r="D69" s="0" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="0" t="s">
+        <v>490</v>
+      </c>
+      <c r="B70" s="0">
+        <v>1301642</v>
+      </c>
+      <c r="C70" s="0">
+        <v>1</v>
+      </c>
+      <c r="D70" s="0" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="0" t="s">
+        <v>491</v>
+      </c>
+      <c r="B71" s="0">
+        <v>685190</v>
+      </c>
+      <c r="C71" s="0">
+        <v>1</v>
+      </c>
+      <c r="D71" s="0" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="0" t="s">
+        <v>492</v>
+      </c>
+      <c r="B72" s="0">
+        <v>407266</v>
+      </c>
+      <c r="C72" s="0">
+        <v>1</v>
+      </c>
+      <c r="D72" s="0" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="0" t="s">
+        <v>493</v>
+      </c>
+      <c r="B73" s="0">
+        <v>1247358</v>
+      </c>
+      <c r="C73" s="0">
+        <v>1</v>
+      </c>
+      <c r="D73" s="0" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="0" t="s">
+        <v>494</v>
+      </c>
+      <c r="B74" s="0">
+        <v>1410088</v>
+      </c>
+      <c r="C74" s="0">
+        <v>1</v>
+      </c>
+      <c r="D74" s="0" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="0" t="s">
+        <v>495</v>
+      </c>
+      <c r="B75" s="0">
+        <v>1410095</v>
+      </c>
+      <c r="C75" s="0">
+        <v>1</v>
+      </c>
+      <c r="D75" s="0" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="0" t="s">
+        <v>496</v>
+      </c>
+      <c r="B76" s="0">
+        <v>1282766</v>
+      </c>
+      <c r="C76" s="0">
+        <v>1</v>
+      </c>
+      <c r="D76" s="0" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="0" t="s">
+        <v>497</v>
+      </c>
+      <c r="B77" s="0">
+        <v>683734</v>
+      </c>
+      <c r="C77" s="0">
+        <v>1</v>
+      </c>
+      <c r="D77" s="0" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="0" t="s">
+        <v>498</v>
+      </c>
+      <c r="B78" s="0">
+        <v>603258</v>
+      </c>
+      <c r="C78" s="0">
+        <v>1</v>
+      </c>
+      <c r="D78" s="0" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="0" t="s">
+        <v>499</v>
+      </c>
+      <c r="B79" s="0">
+        <v>1152871</v>
+      </c>
+      <c r="C79" s="0">
+        <v>1</v>
+      </c>
+      <c r="D79" s="0" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="0" t="s">
+        <v>500</v>
+      </c>
+      <c r="B80" s="0">
+        <v>1425564</v>
+      </c>
+      <c r="C80" s="0">
+        <v>1</v>
+      </c>
+      <c r="D80" s="0" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="0" t="s">
+        <v>501</v>
+      </c>
+      <c r="B81" s="0">
+        <v>1291171</v>
+      </c>
+      <c r="C81" s="0">
+        <v>1</v>
+      </c>
+      <c r="D81" s="0" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="0" t="s">
+        <v>502</v>
+      </c>
+      <c r="B82" s="0">
+        <v>562380</v>
+      </c>
+      <c r="C82" s="0">
+        <v>1</v>
+      </c>
+      <c r="D82" s="0" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="0" t="s">
+        <v>503</v>
+      </c>
+      <c r="B83" s="0">
+        <v>1245770</v>
+      </c>
+      <c r="C83" s="0">
+        <v>1</v>
+      </c>
+      <c r="D83" s="0" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="0" t="s">
+        <v>504</v>
+      </c>
+      <c r="B84" s="0">
+        <v>1432537</v>
+      </c>
+      <c r="C84" s="0">
+        <v>1</v>
+      </c>
+      <c r="D84" s="0" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="0" t="s">
+        <v>505</v>
+      </c>
+      <c r="B85" s="0">
+        <v>619910</v>
+      </c>
+      <c r="C85" s="0">
+        <v>1</v>
+      </c>
+      <c r="D85" s="0" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="0" t="s">
+        <v>506</v>
+      </c>
+      <c r="B86" s="0">
+        <v>1436311</v>
+      </c>
+      <c r="C86" s="0">
+        <v>1</v>
+      </c>
+      <c r="D86" s="0" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="0" t="s">
+        <v>507</v>
+      </c>
+      <c r="B87" s="0">
+        <v>1438402</v>
+      </c>
+      <c r="C87" s="0">
+        <v>1</v>
+      </c>
+      <c r="D87" s="0" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="0" t="s">
+        <v>508</v>
+      </c>
+      <c r="B88" s="0">
+        <v>1441531</v>
+      </c>
+      <c r="C88" s="0">
+        <v>1</v>
+      </c>
+      <c r="D88" s="0" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="0" t="s">
+        <v>509</v>
+      </c>
+      <c r="B89" s="0">
+        <v>1440992</v>
+      </c>
+      <c r="C89" s="0">
+        <v>1</v>
+      </c>
+      <c r="D89" s="0" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="0" t="s">
+        <v>510</v>
+      </c>
+      <c r="B90" s="0">
+        <v>1444686</v>
+      </c>
+      <c r="C90" s="0">
+        <v>1</v>
+      </c>
+      <c r="D90" s="0" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="0" t="s">
+        <v>511</v>
+      </c>
+      <c r="B91" s="0">
+        <v>1446165</v>
+      </c>
+      <c r="C91" s="0">
+        <v>1</v>
+      </c>
+      <c r="D91" s="0" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="0" t="s">
+        <v>512</v>
+      </c>
+      <c r="B92" s="0">
+        <v>1446161</v>
+      </c>
+      <c r="C92" s="0">
+        <v>1</v>
+      </c>
+      <c r="D92" s="0" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="0" t="s">
+        <v>513</v>
+      </c>
+      <c r="B93" s="0">
+        <v>1378826</v>
+      </c>
+      <c r="C93" s="0">
+        <v>1</v>
+      </c>
+      <c r="D93" s="0" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="0" t="s">
+        <v>514</v>
+      </c>
+      <c r="B94" s="0">
+        <v>1447543</v>
+      </c>
+      <c r="C94" s="0">
+        <v>1</v>
+      </c>
+      <c r="D94" s="0" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="0" t="s">
+        <v>515</v>
+      </c>
+      <c r="B95" s="0">
+        <v>1378887</v>
+      </c>
+      <c r="C95" s="0">
+        <v>1</v>
+      </c>
+      <c r="D95" s="0" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="0" t="s">
+        <v>516</v>
+      </c>
+      <c r="B96" s="0">
+        <v>694984</v>
+      </c>
+      <c r="C96" s="0">
+        <v>1</v>
+      </c>
+      <c r="D96" s="0" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="0" t="s">
+        <v>517</v>
+      </c>
+      <c r="B97" s="0">
+        <v>640987</v>
+      </c>
+      <c r="C97" s="0">
+        <v>1</v>
+      </c>
+      <c r="D97" s="0" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="0" t="s">
+        <v>518</v>
+      </c>
+      <c r="B98" s="0">
+        <v>653250</v>
+      </c>
+      <c r="C98" s="0">
+        <v>1</v>
+      </c>
+      <c r="D98" s="0" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="0" t="s">
+        <v>519</v>
+      </c>
+      <c r="B99" s="0">
+        <v>1047913</v>
+      </c>
+      <c r="C99" s="0">
+        <v>1</v>
+      </c>
+      <c r="D99" s="0" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="0" t="s">
+        <v>520</v>
+      </c>
+      <c r="B100" s="0">
+        <v>1450411</v>
+      </c>
+      <c r="C100" s="0">
+        <v>1</v>
+      </c>
+      <c r="D100" s="0" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="0" t="s">
+        <v>521</v>
+      </c>
+      <c r="B101" s="0">
+        <v>1452731</v>
+      </c>
+      <c r="C101" s="0">
+        <v>1</v>
+      </c>
+      <c r="D101" s="0" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="0" t="s">
+        <v>522</v>
+      </c>
+      <c r="B102" s="0">
+        <v>450253</v>
+      </c>
+      <c r="C102" s="0">
+        <v>1</v>
+      </c>
+      <c r="D102" s="0" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="0" t="s">
+        <v>523</v>
+      </c>
+      <c r="B103" s="0">
+        <v>663142</v>
+      </c>
+      <c r="C103" s="0">
+        <v>1</v>
+      </c>
+      <c r="D103" s="0" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="0" t="s">
+        <v>524</v>
+      </c>
+      <c r="B104" s="0">
+        <v>1141554</v>
+      </c>
+      <c r="C104" s="0">
+        <v>1</v>
+      </c>
+      <c r="D104" s="0" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="0" t="s">
+        <v>525</v>
+      </c>
+      <c r="B105" s="0">
+        <v>657422</v>
+      </c>
+      <c r="C105" s="0">
+        <v>1</v>
+      </c>
+      <c r="D105" s="0" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="0" t="s">
+        <v>526</v>
+      </c>
+      <c r="B106" s="0">
+        <v>119771</v>
+      </c>
+      <c r="C106" s="0">
+        <v>1</v>
+      </c>
+      <c r="D106" s="0" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="0" t="s">
+        <v>527</v>
+      </c>
+      <c r="B107" s="0">
+        <v>120131</v>
+      </c>
+      <c r="C107" s="0">
+        <v>1</v>
+      </c>
+      <c r="D107" s="0" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="0" t="s">
+        <v>528</v>
+      </c>
+      <c r="B108" s="0">
+        <v>150022</v>
+      </c>
+      <c r="C108" s="0">
+        <v>1</v>
+      </c>
+      <c r="D108" s="0" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="0" t="s">
+        <v>529</v>
+      </c>
+      <c r="B109" s="0">
+        <v>120677</v>
+      </c>
+      <c r="C109" s="0">
+        <v>1</v>
+      </c>
+      <c r="D109" s="0" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="0" t="s">
+        <v>530</v>
+      </c>
+      <c r="B110" s="0">
+        <v>123824</v>
+      </c>
+      <c r="C110" s="0">
+        <v>1</v>
+      </c>
+      <c r="D110" s="0" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="0" t="s">
+        <v>531</v>
+      </c>
+      <c r="B111" s="0">
+        <v>120257</v>
+      </c>
+      <c r="C111" s="0">
+        <v>1</v>
+      </c>
+      <c r="D111" s="0" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="0" t="s">
+        <v>532</v>
+      </c>
+      <c r="B112" s="0">
+        <v>120054</v>
+      </c>
+      <c r="C112" s="0">
+        <v>1</v>
+      </c>
+      <c r="D112" s="0" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="0" t="s">
+        <v>533</v>
+      </c>
+      <c r="B113" s="0">
+        <v>119809</v>
+      </c>
+      <c r="C113" s="0">
+        <v>1</v>
+      </c>
+      <c r="D113" s="0" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="0" t="s">
+        <v>534</v>
+      </c>
+      <c r="B114" s="0">
+        <v>120713</v>
+      </c>
+      <c r="C114" s="0">
+        <v>1</v>
+      </c>
+      <c r="D114" s="0" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="0" t="s">
+        <v>535</v>
+      </c>
+      <c r="B115" s="0">
+        <v>123458</v>
+      </c>
+      <c r="C115" s="0">
+        <v>1</v>
+      </c>
+      <c r="D115" s="0" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="0" t="s">
+        <v>536</v>
+      </c>
+      <c r="B116" s="0">
+        <v>123644</v>
+      </c>
+      <c r="C116" s="0">
+        <v>1</v>
+      </c>
+      <c r="D116" s="0" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="0" t="s">
+        <v>537</v>
+      </c>
+      <c r="B117" s="0">
+        <v>450256</v>
+      </c>
+      <c r="C117" s="0">
+        <v>1</v>
+      </c>
+      <c r="D117" s="0" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="0" t="s">
+        <v>538</v>
+      </c>
+      <c r="B118" s="0">
+        <v>430463</v>
+      </c>
+      <c r="C118" s="0">
+        <v>1</v>
+      </c>
+      <c r="D118" s="0" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="0" t="s">
+        <v>539</v>
+      </c>
+      <c r="B119" s="0">
+        <v>452188</v>
+      </c>
+      <c r="C119" s="0">
+        <v>1</v>
+      </c>
+      <c r="D119" s="0" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="0" t="s">
+        <v>540</v>
+      </c>
+      <c r="B120" s="0">
+        <v>450695</v>
+      </c>
+      <c r="C120" s="0">
+        <v>1</v>
+      </c>
+      <c r="D120" s="0" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="0" t="s">
+        <v>541</v>
+      </c>
+      <c r="B121" s="0">
+        <v>518459</v>
+      </c>
+      <c r="C121" s="0">
+        <v>1</v>
+      </c>
+      <c r="D121" s="0" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="0" t="s">
+        <v>542</v>
+      </c>
+      <c r="B122" s="0">
+        <v>538810</v>
+      </c>
+      <c r="C122" s="0">
+        <v>1</v>
+      </c>
+      <c r="D122" s="0" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="0" t="s">
+        <v>543</v>
+      </c>
+      <c r="B123" s="0">
+        <v>554080</v>
+      </c>
+      <c r="C123" s="0">
+        <v>1</v>
+      </c>
+      <c r="D123" s="0" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="0" t="s">
+        <v>544</v>
+      </c>
+      <c r="B124" s="0">
+        <v>563370</v>
+      </c>
+      <c r="C124" s="0">
+        <v>1</v>
+      </c>
+      <c r="D124" s="0" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="0" t="s">
+        <v>545</v>
+      </c>
+      <c r="B125" s="0">
+        <v>562860</v>
+      </c>
+      <c r="C125" s="0">
+        <v>1</v>
+      </c>
+      <c r="D125" s="0" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="0" t="s">
+        <v>546</v>
+      </c>
+      <c r="B126" s="0">
+        <v>574529</v>
+      </c>
+      <c r="C126" s="0">
+        <v>1</v>
+      </c>
+      <c r="D126" s="0" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="0" t="s">
+        <v>547</v>
+      </c>
+      <c r="B127" s="0">
+        <v>116683</v>
+      </c>
+      <c r="C127" s="0">
+        <v>1</v>
+      </c>
+      <c r="D127" s="0" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="0" t="s">
+        <v>548</v>
+      </c>
+      <c r="B128" s="0">
+        <v>622048</v>
+      </c>
+      <c r="C128" s="0">
+        <v>1</v>
+      </c>
+      <c r="D128" s="0" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="0" t="s">
+        <v>549</v>
+      </c>
+      <c r="B129" s="0">
+        <v>570705</v>
+      </c>
+      <c r="C129" s="0">
+        <v>1</v>
+      </c>
+      <c r="D129" s="0" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="0" t="s">
+        <v>550</v>
+      </c>
+      <c r="B130" s="0">
+        <v>622041</v>
+      </c>
+      <c r="C130" s="0">
+        <v>1</v>
+      </c>
+      <c r="D130" s="0" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="0" t="s">
+        <v>551</v>
+      </c>
+      <c r="B131" s="0">
+        <v>622038</v>
+      </c>
+      <c r="C131" s="0">
+        <v>1</v>
+      </c>
+      <c r="D131" s="0" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="0" t="s">
+        <v>552</v>
+      </c>
+      <c r="B132" s="0">
+        <v>622049</v>
+      </c>
+      <c r="C132" s="0">
+        <v>1</v>
+      </c>
+      <c r="D132" s="0" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="0" t="s">
+        <v>553</v>
+      </c>
+      <c r="B133" s="0">
+        <v>624345</v>
+      </c>
+      <c r="C133" s="0">
+        <v>1</v>
+      </c>
+      <c r="D133" s="0" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="0" t="s">
+        <v>554</v>
+      </c>
+      <c r="B134" s="0">
+        <v>405581</v>
+      </c>
+      <c r="C134" s="0">
+        <v>1</v>
+      </c>
+      <c r="D134" s="0" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="0" t="s">
+        <v>555</v>
+      </c>
+      <c r="B135" s="0">
+        <v>625715</v>
+      </c>
+      <c r="C135" s="0">
+        <v>1</v>
+      </c>
+      <c r="D135" s="0" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="0" t="s">
+        <v>556</v>
+      </c>
+      <c r="B136" s="0">
+        <v>625719</v>
+      </c>
+      <c r="C136" s="0">
+        <v>1</v>
+      </c>
+      <c r="D136" s="0" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="0" t="s">
+        <v>557</v>
+      </c>
+      <c r="B137" s="0">
+        <v>625726</v>
+      </c>
+      <c r="C137" s="0">
+        <v>1</v>
+      </c>
+      <c r="D137" s="0" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="0" t="s">
+        <v>558</v>
+      </c>
+      <c r="B138" s="0">
+        <v>596585</v>
+      </c>
+      <c r="C138" s="0">
+        <v>1</v>
+      </c>
+      <c r="D138" s="0" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="0" t="s">
+        <v>559</v>
+      </c>
+      <c r="B139" s="0">
+        <v>527369</v>
+      </c>
+      <c r="C139" s="0">
+        <v>1</v>
+      </c>
+      <c r="D139" s="0" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="0" t="s">
+        <v>560</v>
+      </c>
+      <c r="B140" s="0">
+        <v>1010813</v>
+      </c>
+      <c r="C140" s="0">
+        <v>1</v>
+      </c>
+      <c r="D140" s="0" t="s">
+        <v>618</v>
       </c>
     </row>
   </sheetData>
@@ -4269,7 +6691,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H88"/>
+  <dimension ref="A1:H94"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.85546875" customWidth="true"/>
@@ -4310,7 +6732,7 @@
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>443</v>
+        <v>647</v>
       </c>
       <c r="B2" s="0" t="s">
         <v>277</v>
@@ -4322,13 +6744,13 @@
         <v>107</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>516</v>
+        <v>726</v>
       </c>
       <c r="F2" s="0" t="s">
-        <v>570</v>
+        <v>777</v>
       </c>
       <c r="G2" s="0" t="s">
-        <v>603</v>
+        <v>812</v>
       </c>
       <c r="H2" s="0">
         <v>6737415</v>
@@ -4336,7 +6758,7 @@
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>443</v>
+        <v>647</v>
       </c>
       <c r="B3" s="0" t="s">
         <v>278</v>
@@ -4348,13 +6770,13 @@
         <v>107</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>516</v>
+        <v>726</v>
       </c>
       <c r="F3" s="0" t="s">
-        <v>570</v>
+        <v>777</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>603</v>
+        <v>812</v>
       </c>
       <c r="H3" s="0">
         <v>6737416</v>
@@ -4362,7 +6784,7 @@
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>444</v>
+        <v>648</v>
       </c>
       <c r="B4" s="0" t="s">
         <v>277</v>
@@ -4374,13 +6796,13 @@
         <v>107</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>517</v>
+        <v>727</v>
       </c>
       <c r="F4" s="0" t="s">
-        <v>571</v>
+        <v>778</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>604</v>
+        <v>813</v>
       </c>
       <c r="H4" s="0">
         <v>18771404</v>
@@ -4388,7 +6810,7 @@
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>444</v>
+        <v>648</v>
       </c>
       <c r="B5" s="0" t="s">
         <v>278</v>
@@ -4400,13 +6822,13 @@
         <v>107</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>517</v>
+        <v>727</v>
       </c>
       <c r="F5" s="0" t="s">
-        <v>571</v>
+        <v>778</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>604</v>
+        <v>813</v>
       </c>
       <c r="H5" s="0">
         <v>18771405</v>
@@ -4414,7 +6836,7 @@
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>445</v>
+        <v>649</v>
       </c>
       <c r="B6" s="0" t="s">
         <v>277</v>
@@ -4426,13 +6848,13 @@
         <v>107</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>518</v>
+        <v>728</v>
       </c>
       <c r="F6" s="0" t="s">
-        <v>572</v>
+        <v>779</v>
       </c>
       <c r="G6" s="0" t="s">
-        <v>605</v>
+        <v>814</v>
       </c>
       <c r="H6" s="0">
         <v>18839472</v>
@@ -4440,7 +6862,7 @@
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>445</v>
+        <v>649</v>
       </c>
       <c r="B7" s="0" t="s">
         <v>278</v>
@@ -4452,13 +6874,13 @@
         <v>107</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>518</v>
+        <v>728</v>
       </c>
       <c r="F7" s="0" t="s">
-        <v>572</v>
+        <v>779</v>
       </c>
       <c r="G7" s="0" t="s">
-        <v>605</v>
+        <v>814</v>
       </c>
       <c r="H7" s="0">
         <v>18839473</v>
@@ -4466,10 +6888,10 @@
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>446</v>
+        <v>650</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>477</v>
+        <v>683</v>
       </c>
       <c r="C8" s="0">
         <v>3200</v>
@@ -4478,13 +6900,13 @@
         <v>107</v>
       </c>
       <c r="E8" s="0" t="s">
-        <v>519</v>
+        <v>729</v>
       </c>
       <c r="F8" s="0" t="s">
-        <v>573</v>
+        <v>780</v>
       </c>
       <c r="G8" s="0" t="s">
-        <v>606</v>
+        <v>815</v>
       </c>
       <c r="H8" s="0">
         <v>677079</v>
@@ -4492,10 +6914,10 @@
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>446</v>
+        <v>650</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>478</v>
+        <v>684</v>
       </c>
       <c r="C9" s="0">
         <v>3100</v>
@@ -4504,13 +6926,13 @@
         <v>107</v>
       </c>
       <c r="E9" s="0" t="s">
-        <v>520</v>
+        <v>730</v>
       </c>
       <c r="F9" s="0" t="s">
-        <v>573</v>
+        <v>780</v>
       </c>
       <c r="G9" s="0" t="s">
-        <v>607</v>
+        <v>816</v>
       </c>
       <c r="H9" s="0">
         <v>677113</v>
@@ -4518,25 +6940,25 @@
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>446</v>
+        <v>650</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>479</v>
+        <v>685</v>
       </c>
       <c r="C10" s="0">
         <v>1100</v>
       </c>
       <c r="D10" s="0">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="E10" s="0" t="s">
-        <v>521</v>
+        <v>731</v>
       </c>
       <c r="F10" s="0" t="s">
         <v>353</v>
       </c>
       <c r="G10" s="0" t="s">
-        <v>608</v>
+        <v>817</v>
       </c>
       <c r="H10" s="0">
         <v>677168</v>
@@ -4544,25 +6966,25 @@
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
-        <v>446</v>
+        <v>650</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>480</v>
+        <v>686</v>
       </c>
       <c r="C11" s="0">
         <v>2100</v>
       </c>
       <c r="D11" s="0">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="E11" s="0" t="s">
-        <v>521</v>
+        <v>731</v>
       </c>
       <c r="F11" s="0" t="s">
         <v>353</v>
       </c>
       <c r="G11" s="0" t="s">
-        <v>608</v>
+        <v>817</v>
       </c>
       <c r="H11" s="0">
         <v>677140</v>
@@ -4570,10 +6992,10 @@
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
-        <v>446</v>
+        <v>650</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>481</v>
+        <v>687</v>
       </c>
       <c r="C12" s="0">
         <v>1100</v>
@@ -4582,13 +7004,13 @@
         <v>107</v>
       </c>
       <c r="E12" s="0" t="s">
-        <v>522</v>
+        <v>732</v>
       </c>
       <c r="F12" s="0" t="s">
-        <v>574</v>
+        <v>781</v>
       </c>
       <c r="G12" s="0" t="s">
-        <v>606</v>
+        <v>815</v>
       </c>
       <c r="H12" s="0">
         <v>677149</v>
@@ -4596,10 +7018,10 @@
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
-        <v>446</v>
+        <v>650</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>482</v>
+        <v>688</v>
       </c>
       <c r="C13" s="0">
         <v>2100</v>
@@ -4608,13 +7030,13 @@
         <v>107</v>
       </c>
       <c r="E13" s="0" t="s">
-        <v>523</v>
+        <v>733</v>
       </c>
       <c r="F13" s="0" t="s">
-        <v>574</v>
+        <v>781</v>
       </c>
       <c r="G13" s="0" t="s">
-        <v>606</v>
+        <v>815</v>
       </c>
       <c r="H13" s="0">
         <v>677148</v>
@@ -4622,7 +7044,7 @@
     </row>
     <row r="14">
       <c r="A14" s="0" t="s">
-        <v>447</v>
+        <v>651</v>
       </c>
       <c r="B14" s="0" t="s">
         <v>277</v>
@@ -4634,13 +7056,13 @@
         <v>107</v>
       </c>
       <c r="E14" s="0" t="s">
-        <v>524</v>
+        <v>734</v>
       </c>
       <c r="F14" s="0" t="s">
-        <v>575</v>
+        <v>782</v>
       </c>
       <c r="G14" s="0" t="s">
-        <v>603</v>
+        <v>812</v>
       </c>
       <c r="H14" s="0">
         <v>6737419</v>
@@ -4648,7 +7070,7 @@
     </row>
     <row r="15">
       <c r="A15" s="0" t="s">
-        <v>447</v>
+        <v>651</v>
       </c>
       <c r="B15" s="0" t="s">
         <v>278</v>
@@ -4660,13 +7082,13 @@
         <v>107</v>
       </c>
       <c r="E15" s="0" t="s">
-        <v>524</v>
+        <v>734</v>
       </c>
       <c r="F15" s="0" t="s">
-        <v>575</v>
+        <v>782</v>
       </c>
       <c r="G15" s="0" t="s">
-        <v>603</v>
+        <v>812</v>
       </c>
       <c r="H15" s="0">
         <v>6737420</v>
@@ -4674,7 +7096,7 @@
     </row>
     <row r="16">
       <c r="A16" s="0" t="s">
-        <v>448</v>
+        <v>652</v>
       </c>
       <c r="B16" s="0" t="s">
         <v>277</v>
@@ -4686,13 +7108,13 @@
         <v>107</v>
       </c>
       <c r="E16" s="0" t="s">
-        <v>525</v>
+        <v>735</v>
       </c>
       <c r="F16" s="0" t="s">
         <v>353</v>
       </c>
       <c r="G16" s="0" t="s">
-        <v>608</v>
+        <v>817</v>
       </c>
       <c r="H16" s="0">
         <v>677105</v>
@@ -4700,7 +7122,7 @@
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
-        <v>448</v>
+        <v>652</v>
       </c>
       <c r="B17" s="0" t="s">
         <v>278</v>
@@ -4712,13 +7134,13 @@
         <v>107</v>
       </c>
       <c r="E17" s="0" t="s">
-        <v>525</v>
+        <v>735</v>
       </c>
       <c r="F17" s="0" t="s">
         <v>353</v>
       </c>
       <c r="G17" s="0" t="s">
-        <v>608</v>
+        <v>817</v>
       </c>
       <c r="H17" s="0">
         <v>677114</v>
@@ -4726,7 +7148,7 @@
     </row>
     <row r="18">
       <c r="A18" s="0" t="s">
-        <v>449</v>
+        <v>653</v>
       </c>
       <c r="B18" s="0" t="s">
         <v>277</v>
@@ -4738,13 +7160,13 @@
         <v>107</v>
       </c>
       <c r="E18" s="0" t="s">
-        <v>526</v>
+        <v>736</v>
       </c>
       <c r="F18" s="0" t="s">
         <v>353</v>
       </c>
       <c r="G18" s="0" t="s">
-        <v>608</v>
+        <v>817</v>
       </c>
       <c r="H18" s="0">
         <v>677153</v>
@@ -4752,7 +7174,7 @@
     </row>
     <row r="19">
       <c r="A19" s="0" t="s">
-        <v>449</v>
+        <v>653</v>
       </c>
       <c r="B19" s="0" t="s">
         <v>278</v>
@@ -4764,13 +7186,13 @@
         <v>107</v>
       </c>
       <c r="E19" s="0" t="s">
-        <v>527</v>
+        <v>737</v>
       </c>
       <c r="F19" s="0" t="s">
         <v>353</v>
       </c>
       <c r="G19" s="0" t="s">
-        <v>608</v>
+        <v>817</v>
       </c>
       <c r="H19" s="0">
         <v>677124</v>
@@ -4778,7 +7200,7 @@
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
-        <v>450</v>
+        <v>654</v>
       </c>
       <c r="B20" s="0" t="s">
         <v>277</v>
@@ -4790,13 +7212,13 @@
         <v>107</v>
       </c>
       <c r="E20" s="0" t="s">
-        <v>528</v>
+        <v>738</v>
       </c>
       <c r="F20" s="0" t="s">
-        <v>576</v>
+        <v>783</v>
       </c>
       <c r="G20" s="0" t="s">
-        <v>609</v>
+        <v>818</v>
       </c>
       <c r="H20" s="0">
         <v>19470810</v>
@@ -4804,7 +7226,7 @@
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
-        <v>450</v>
+        <v>654</v>
       </c>
       <c r="B21" s="0" t="s">
         <v>278</v>
@@ -4816,13 +7238,13 @@
         <v>107</v>
       </c>
       <c r="E21" s="0" t="s">
-        <v>528</v>
+        <v>738</v>
       </c>
       <c r="F21" s="0" t="s">
-        <v>576</v>
+        <v>783</v>
       </c>
       <c r="G21" s="0" t="s">
-        <v>609</v>
+        <v>818</v>
       </c>
       <c r="H21" s="0">
         <v>19470811</v>
@@ -4830,10 +7252,10 @@
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
-        <v>451</v>
+        <v>655</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>483</v>
+        <v>689</v>
       </c>
       <c r="C22" s="0">
         <v>2100</v>
@@ -4842,13 +7264,13 @@
         <v>107</v>
       </c>
       <c r="E22" s="0" t="s">
-        <v>529</v>
+        <v>739</v>
       </c>
       <c r="F22" s="0" t="s">
-        <v>577</v>
+        <v>784</v>
       </c>
       <c r="G22" s="0" t="s">
-        <v>610</v>
+        <v>819</v>
       </c>
       <c r="H22" s="0">
         <v>677138</v>
@@ -4856,10 +7278,10 @@
     </row>
     <row r="23">
       <c r="A23" s="0" t="s">
-        <v>451</v>
+        <v>655</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>484</v>
+        <v>690</v>
       </c>
       <c r="C23" s="0">
         <v>1100</v>
@@ -4868,13 +7290,13 @@
         <v>107</v>
       </c>
       <c r="E23" s="0" t="s">
-        <v>529</v>
+        <v>739</v>
       </c>
       <c r="F23" s="0" t="s">
-        <v>578</v>
+        <v>785</v>
       </c>
       <c r="G23" s="0" t="s">
-        <v>610</v>
+        <v>819</v>
       </c>
       <c r="H23" s="0">
         <v>677141</v>
@@ -4882,10 +7304,10 @@
     </row>
     <row r="24">
       <c r="A24" s="0" t="s">
-        <v>451</v>
+        <v>655</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>485</v>
+        <v>691</v>
       </c>
       <c r="C24" s="0">
         <v>2100</v>
@@ -4894,13 +7316,13 @@
         <v>107</v>
       </c>
       <c r="E24" s="0" t="s">
-        <v>529</v>
+        <v>739</v>
       </c>
       <c r="F24" s="0" t="s">
-        <v>578</v>
+        <v>785</v>
       </c>
       <c r="G24" s="0" t="s">
-        <v>610</v>
+        <v>819</v>
       </c>
       <c r="H24" s="0">
         <v>677150</v>
@@ -4908,10 +7330,10 @@
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
-        <v>452</v>
+        <v>656</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>486</v>
+        <v>692</v>
       </c>
       <c r="C25" s="0">
         <v>1100</v>
@@ -4920,13 +7342,13 @@
         <v>107</v>
       </c>
       <c r="E25" s="0" t="s">
-        <v>530</v>
+        <v>740</v>
       </c>
       <c r="F25" s="0" t="s">
-        <v>579</v>
+        <v>786</v>
       </c>
       <c r="G25" s="0" t="s">
-        <v>611</v>
+        <v>820</v>
       </c>
       <c r="H25" s="0">
         <v>9697138</v>
@@ -4934,10 +7356,10 @@
     </row>
     <row r="26">
       <c r="A26" s="0" t="s">
-        <v>452</v>
+        <v>656</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>487</v>
+        <v>693</v>
       </c>
       <c r="C26" s="0">
         <v>2100</v>
@@ -4946,13 +7368,13 @@
         <v>107</v>
       </c>
       <c r="E26" s="0" t="s">
-        <v>530</v>
+        <v>740</v>
       </c>
       <c r="F26" s="0" t="s">
-        <v>579</v>
+        <v>786</v>
       </c>
       <c r="G26" s="0" t="s">
-        <v>611</v>
+        <v>820</v>
       </c>
       <c r="H26" s="0">
         <v>9697137</v>
@@ -4960,10 +7382,10 @@
     </row>
     <row r="27">
       <c r="A27" s="0" t="s">
-        <v>452</v>
+        <v>656</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>488</v>
+        <v>694</v>
       </c>
       <c r="C27" s="0">
         <v>1100</v>
@@ -4972,13 +7394,13 @@
         <v>107</v>
       </c>
       <c r="E27" s="0" t="s">
-        <v>531</v>
+        <v>741</v>
       </c>
       <c r="F27" s="0" t="s">
-        <v>580</v>
+        <v>787</v>
       </c>
       <c r="G27" s="0" t="s">
-        <v>612</v>
+        <v>821</v>
       </c>
       <c r="H27" s="0">
         <v>18772023</v>
@@ -4986,10 +7408,10 @@
     </row>
     <row r="28">
       <c r="A28" s="0" t="s">
-        <v>452</v>
+        <v>656</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>489</v>
+        <v>695</v>
       </c>
       <c r="C28" s="0">
         <v>2100</v>
@@ -4998,13 +7420,13 @@
         <v>107</v>
       </c>
       <c r="E28" s="0" t="s">
-        <v>531</v>
+        <v>741</v>
       </c>
       <c r="F28" s="0" t="s">
-        <v>580</v>
+        <v>787</v>
       </c>
       <c r="G28" s="0" t="s">
-        <v>612</v>
+        <v>821</v>
       </c>
       <c r="H28" s="0">
         <v>18772024</v>
@@ -5012,10 +7434,10 @@
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
-        <v>453</v>
+        <v>657</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>490</v>
+        <v>696</v>
       </c>
       <c r="C29" s="0">
         <v>3400</v>
@@ -5024,13 +7446,13 @@
         <v>107</v>
       </c>
       <c r="E29" s="0" t="s">
-        <v>532</v>
+        <v>742</v>
       </c>
       <c r="F29" s="0" t="s">
-        <v>581</v>
+        <v>788</v>
       </c>
       <c r="G29" s="0" t="s">
-        <v>613</v>
+        <v>822</v>
       </c>
       <c r="H29" s="0">
         <v>18772025</v>
@@ -5038,7 +7460,7 @@
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
-        <v>454</v>
+        <v>658</v>
       </c>
       <c r="B30" s="0" t="s">
         <v>277</v>
@@ -5050,13 +7472,13 @@
         <v>107</v>
       </c>
       <c r="E30" s="0" t="s">
-        <v>533</v>
+        <v>743</v>
       </c>
       <c r="F30" s="0" t="s">
-        <v>582</v>
+        <v>789</v>
       </c>
       <c r="G30" s="0" t="s">
-        <v>614</v>
+        <v>823</v>
       </c>
       <c r="H30" s="0">
         <v>19289126</v>
@@ -5064,7 +7486,7 @@
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
-        <v>454</v>
+        <v>658</v>
       </c>
       <c r="B31" s="0" t="s">
         <v>278</v>
@@ -5076,13 +7498,13 @@
         <v>107</v>
       </c>
       <c r="E31" s="0" t="s">
-        <v>534</v>
+        <v>744</v>
       </c>
       <c r="F31" s="0" t="s">
-        <v>582</v>
+        <v>789</v>
       </c>
       <c r="G31" s="0" t="s">
-        <v>608</v>
+        <v>817</v>
       </c>
       <c r="H31" s="0">
         <v>19289125</v>
@@ -5090,7 +7512,7 @@
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
-        <v>455</v>
+        <v>659</v>
       </c>
       <c r="B32" s="0" t="s">
         <v>277</v>
@@ -5099,16 +7521,16 @@
         <v>1100</v>
       </c>
       <c r="D32" s="0">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="E32" s="0" t="s">
-        <v>535</v>
+        <v>745</v>
       </c>
       <c r="F32" s="0" t="s">
-        <v>583</v>
+        <v>790</v>
       </c>
       <c r="G32" s="0" t="s">
-        <v>615</v>
+        <v>824</v>
       </c>
       <c r="H32" s="0">
         <v>18748267</v>
@@ -5116,7 +7538,7 @@
     </row>
     <row r="33">
       <c r="A33" s="0" t="s">
-        <v>455</v>
+        <v>659</v>
       </c>
       <c r="B33" s="0" t="s">
         <v>278</v>
@@ -5125,16 +7547,16 @@
         <v>2100</v>
       </c>
       <c r="D33" s="0">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="E33" s="0" t="s">
-        <v>535</v>
+        <v>745</v>
       </c>
       <c r="F33" s="0" t="s">
-        <v>583</v>
+        <v>790</v>
       </c>
       <c r="G33" s="0" t="s">
-        <v>615</v>
+        <v>824</v>
       </c>
       <c r="H33" s="0">
         <v>18748268</v>
@@ -5142,25 +7564,25 @@
     </row>
     <row r="34">
       <c r="A34" s="0" t="s">
-        <v>456</v>
+        <v>660</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>491</v>
+        <v>697</v>
       </c>
       <c r="C34" s="0">
         <v>1100</v>
       </c>
       <c r="D34" s="0">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="E34" s="0" t="s">
-        <v>536</v>
+        <v>746</v>
       </c>
       <c r="F34" s="0" t="s">
-        <v>579</v>
+        <v>786</v>
       </c>
       <c r="G34" s="0" t="s">
-        <v>611</v>
+        <v>820</v>
       </c>
       <c r="H34" s="0">
         <v>18748269</v>
@@ -5168,25 +7590,25 @@
     </row>
     <row r="35">
       <c r="A35" s="0" t="s">
-        <v>456</v>
+        <v>660</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>492</v>
+        <v>698</v>
       </c>
       <c r="C35" s="0">
         <v>2100</v>
       </c>
       <c r="D35" s="0">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="E35" s="0" t="s">
-        <v>536</v>
+        <v>746</v>
       </c>
       <c r="F35" s="0" t="s">
-        <v>579</v>
+        <v>786</v>
       </c>
       <c r="G35" s="0" t="s">
-        <v>611</v>
+        <v>820</v>
       </c>
       <c r="H35" s="0">
         <v>18748270</v>
@@ -5194,25 +7616,25 @@
     </row>
     <row r="36">
       <c r="A36" s="0" t="s">
-        <v>456</v>
+        <v>660</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>493</v>
+        <v>699</v>
       </c>
       <c r="C36" s="0">
         <v>1100</v>
       </c>
       <c r="D36" s="0">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="E36" s="0" t="s">
-        <v>536</v>
+        <v>746</v>
       </c>
       <c r="F36" s="0" t="s">
-        <v>584</v>
+        <v>791</v>
       </c>
       <c r="G36" s="0" t="s">
-        <v>611</v>
+        <v>820</v>
       </c>
       <c r="H36" s="0">
         <v>18748271</v>
@@ -5220,25 +7642,25 @@
     </row>
     <row r="37">
       <c r="A37" s="0" t="s">
-        <v>456</v>
+        <v>660</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>494</v>
+        <v>700</v>
       </c>
       <c r="C37" s="0">
         <v>2100</v>
       </c>
       <c r="D37" s="0">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="E37" s="0" t="s">
-        <v>536</v>
+        <v>746</v>
       </c>
       <c r="F37" s="0" t="s">
-        <v>584</v>
+        <v>791</v>
       </c>
       <c r="G37" s="0" t="s">
-        <v>611</v>
+        <v>820</v>
       </c>
       <c r="H37" s="0">
         <v>18748272</v>
@@ -5246,7 +7668,7 @@
     </row>
     <row r="38">
       <c r="A38" s="0" t="s">
-        <v>457</v>
+        <v>661</v>
       </c>
       <c r="B38" s="0" t="s">
         <v>277</v>
@@ -5258,13 +7680,13 @@
         <v>107</v>
       </c>
       <c r="E38" s="0" t="s">
-        <v>537</v>
+        <v>747</v>
       </c>
       <c r="F38" s="0" t="s">
-        <v>585</v>
+        <v>792</v>
       </c>
       <c r="G38" s="0" t="s">
-        <v>611</v>
+        <v>820</v>
       </c>
       <c r="H38" s="0">
         <v>18905788</v>
@@ -5272,7 +7694,7 @@
     </row>
     <row r="39">
       <c r="A39" s="0" t="s">
-        <v>457</v>
+        <v>661</v>
       </c>
       <c r="B39" s="0" t="s">
         <v>278</v>
@@ -5284,13 +7706,13 @@
         <v>107</v>
       </c>
       <c r="E39" s="0" t="s">
-        <v>537</v>
+        <v>747</v>
       </c>
       <c r="F39" s="0" t="s">
-        <v>585</v>
+        <v>792</v>
       </c>
       <c r="G39" s="0" t="s">
-        <v>611</v>
+        <v>820</v>
       </c>
       <c r="H39" s="0">
         <v>18905787</v>
@@ -5298,10 +7720,10 @@
     </row>
     <row r="40">
       <c r="A40" s="0" t="s">
-        <v>458</v>
+        <v>662</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>277</v>
+        <v>701</v>
       </c>
       <c r="C40" s="0">
         <v>1100</v>
@@ -5310,13 +7732,13 @@
         <v>107</v>
       </c>
       <c r="E40" s="0" t="s">
-        <v>538</v>
+        <v>748</v>
       </c>
       <c r="F40" s="0" t="s">
-        <v>586</v>
+        <v>793</v>
       </c>
       <c r="G40" s="0" t="s">
-        <v>616</v>
+        <v>825</v>
       </c>
       <c r="H40" s="0">
         <v>6737417</v>
@@ -5324,10 +7746,10 @@
     </row>
     <row r="41">
       <c r="A41" s="0" t="s">
-        <v>458</v>
+        <v>662</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>278</v>
+        <v>702</v>
       </c>
       <c r="C41" s="0">
         <v>2100</v>
@@ -5336,13 +7758,13 @@
         <v>107</v>
       </c>
       <c r="E41" s="0" t="s">
-        <v>539</v>
+        <v>748</v>
       </c>
       <c r="F41" s="0" t="s">
-        <v>586</v>
+        <v>793</v>
       </c>
       <c r="G41" s="0" t="s">
-        <v>616</v>
+        <v>825</v>
       </c>
       <c r="H41" s="0">
         <v>6737418</v>
@@ -5350,10 +7772,10 @@
     </row>
     <row r="42">
       <c r="A42" s="0" t="s">
-        <v>459</v>
+        <v>662</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>495</v>
+        <v>703</v>
       </c>
       <c r="C42" s="0">
         <v>1100</v>
@@ -5362,24 +7784,24 @@
         <v>107</v>
       </c>
       <c r="E42" s="0" t="s">
-        <v>540</v>
+        <v>748</v>
       </c>
       <c r="F42" s="0" t="s">
-        <v>587</v>
+        <v>794</v>
       </c>
       <c r="G42" s="0" t="s">
-        <v>617</v>
+        <v>825</v>
       </c>
       <c r="H42" s="0">
-        <v>19044113</v>
+        <v>11111111</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="0" t="s">
-        <v>459</v>
+        <v>662</v>
       </c>
       <c r="B43" s="0" t="s">
-        <v>496</v>
+        <v>704</v>
       </c>
       <c r="C43" s="0">
         <v>2100</v>
@@ -5388,24 +7810,24 @@
         <v>107</v>
       </c>
       <c r="E43" s="0" t="s">
-        <v>541</v>
+        <v>748</v>
       </c>
       <c r="F43" s="0" t="s">
-        <v>587</v>
+        <v>794</v>
       </c>
       <c r="G43" s="0" t="s">
-        <v>618</v>
+        <v>825</v>
       </c>
       <c r="H43" s="0">
-        <v>19044114</v>
+        <v>11111111</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="0" t="s">
-        <v>459</v>
+        <v>663</v>
       </c>
       <c r="B44" s="0" t="s">
-        <v>497</v>
+        <v>705</v>
       </c>
       <c r="C44" s="0">
         <v>1100</v>
@@ -5414,24 +7836,24 @@
         <v>107</v>
       </c>
       <c r="E44" s="0" t="s">
-        <v>542</v>
+        <v>749</v>
       </c>
       <c r="F44" s="0" t="s">
-        <v>588</v>
+        <v>795</v>
       </c>
       <c r="G44" s="0" t="s">
-        <v>618</v>
+        <v>826</v>
       </c>
       <c r="H44" s="0">
-        <v>19044115</v>
+        <v>19044113</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="0" t="s">
-        <v>459</v>
+        <v>663</v>
       </c>
       <c r="B45" s="0" t="s">
-        <v>498</v>
+        <v>706</v>
       </c>
       <c r="C45" s="0">
         <v>2100</v>
@@ -5440,24 +7862,24 @@
         <v>107</v>
       </c>
       <c r="E45" s="0" t="s">
-        <v>543</v>
+        <v>750</v>
       </c>
       <c r="F45" s="0" t="s">
-        <v>588</v>
+        <v>795</v>
       </c>
       <c r="G45" s="0" t="s">
-        <v>608</v>
+        <v>826</v>
       </c>
       <c r="H45" s="0">
-        <v>19044116</v>
+        <v>19044114</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="0" t="s">
-        <v>460</v>
+        <v>663</v>
       </c>
       <c r="B46" s="0" t="s">
-        <v>277</v>
+        <v>707</v>
       </c>
       <c r="C46" s="0">
         <v>1100</v>
@@ -5466,24 +7888,24 @@
         <v>107</v>
       </c>
       <c r="E46" s="0" t="s">
-        <v>544</v>
+        <v>751</v>
       </c>
       <c r="F46" s="0" t="s">
-        <v>589</v>
+        <v>796</v>
       </c>
       <c r="G46" s="0" t="s">
-        <v>619</v>
+        <v>827</v>
       </c>
       <c r="H46" s="0">
-        <v>18905782</v>
+        <v>19044115</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="0" t="s">
-        <v>460</v>
+        <v>663</v>
       </c>
       <c r="B47" s="0" t="s">
-        <v>278</v>
+        <v>708</v>
       </c>
       <c r="C47" s="0">
         <v>2100</v>
@@ -5492,21 +7914,21 @@
         <v>107</v>
       </c>
       <c r="E47" s="0" t="s">
-        <v>544</v>
+        <v>751</v>
       </c>
       <c r="F47" s="0" t="s">
-        <v>589</v>
+        <v>796</v>
       </c>
       <c r="G47" s="0" t="s">
-        <v>619</v>
+        <v>827</v>
       </c>
       <c r="H47" s="0">
-        <v>18905781</v>
+        <v>19044116</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="0" t="s">
-        <v>461</v>
+        <v>664</v>
       </c>
       <c r="B48" s="0" t="s">
         <v>277</v>
@@ -5518,21 +7940,21 @@
         <v>107</v>
       </c>
       <c r="E48" s="0" t="s">
-        <v>545</v>
+        <v>752</v>
       </c>
       <c r="F48" s="0" t="s">
-        <v>590</v>
+        <v>797</v>
       </c>
       <c r="G48" s="0" t="s">
-        <v>614</v>
+        <v>828</v>
       </c>
       <c r="H48" s="0">
-        <v>19865894</v>
+        <v>18905782</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="0" t="s">
-        <v>461</v>
+        <v>664</v>
       </c>
       <c r="B49" s="0" t="s">
         <v>278</v>
@@ -5544,24 +7966,24 @@
         <v>107</v>
       </c>
       <c r="E49" s="0" t="s">
-        <v>545</v>
+        <v>752</v>
       </c>
       <c r="F49" s="0" t="s">
-        <v>590</v>
+        <v>797</v>
       </c>
       <c r="G49" s="0" t="s">
-        <v>614</v>
+        <v>828</v>
       </c>
       <c r="H49" s="0">
-        <v>19865893</v>
+        <v>18905781</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="0" t="s">
-        <v>462</v>
+        <v>665</v>
       </c>
       <c r="B50" s="0" t="s">
-        <v>499</v>
+        <v>277</v>
       </c>
       <c r="C50" s="0">
         <v>1100</v>
@@ -5570,24 +7992,24 @@
         <v>107</v>
       </c>
       <c r="E50" s="0" t="s">
-        <v>546</v>
+        <v>753</v>
       </c>
       <c r="F50" s="0" t="s">
-        <v>591</v>
+        <v>798</v>
       </c>
       <c r="G50" s="0" t="s">
-        <v>620</v>
+        <v>823</v>
       </c>
       <c r="H50" s="0">
-        <v>10367489</v>
+        <v>19865894</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="0" t="s">
-        <v>462</v>
+        <v>665</v>
       </c>
       <c r="B51" s="0" t="s">
-        <v>500</v>
+        <v>278</v>
       </c>
       <c r="C51" s="0">
         <v>2100</v>
@@ -5596,24 +8018,24 @@
         <v>107</v>
       </c>
       <c r="E51" s="0" t="s">
-        <v>546</v>
+        <v>753</v>
       </c>
       <c r="F51" s="0" t="s">
-        <v>591</v>
+        <v>798</v>
       </c>
       <c r="G51" s="0" t="s">
-        <v>620</v>
+        <v>823</v>
       </c>
       <c r="H51" s="0">
-        <v>10367490</v>
+        <v>19865893</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="0" t="s">
-        <v>462</v>
+        <v>666</v>
       </c>
       <c r="B52" s="0" t="s">
-        <v>501</v>
+        <v>709</v>
       </c>
       <c r="C52" s="0">
         <v>1100</v>
@@ -5622,24 +8044,24 @@
         <v>107</v>
       </c>
       <c r="E52" s="0" t="s">
-        <v>547</v>
+        <v>754</v>
       </c>
       <c r="F52" s="0" t="s">
-        <v>592</v>
+        <v>799</v>
       </c>
       <c r="G52" s="0" t="s">
-        <v>621</v>
+        <v>829</v>
       </c>
       <c r="H52" s="0">
-        <v>10367491</v>
+        <v>10367489</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="0" t="s">
-        <v>462</v>
+        <v>666</v>
       </c>
       <c r="B53" s="0" t="s">
-        <v>502</v>
+        <v>710</v>
       </c>
       <c r="C53" s="0">
         <v>2100</v>
@@ -5648,24 +8070,24 @@
         <v>107</v>
       </c>
       <c r="E53" s="0" t="s">
-        <v>548</v>
+        <v>754</v>
       </c>
       <c r="F53" s="0" t="s">
-        <v>592</v>
+        <v>799</v>
       </c>
       <c r="G53" s="0" t="s">
-        <v>621</v>
+        <v>829</v>
       </c>
       <c r="H53" s="0">
-        <v>10367492</v>
+        <v>10367490</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="0" t="s">
-        <v>463</v>
+        <v>666</v>
       </c>
       <c r="B54" s="0" t="s">
-        <v>277</v>
+        <v>711</v>
       </c>
       <c r="C54" s="0">
         <v>1100</v>
@@ -5674,24 +8096,24 @@
         <v>107</v>
       </c>
       <c r="E54" s="0" t="s">
-        <v>549</v>
+        <v>755</v>
       </c>
       <c r="F54" s="0" t="s">
-        <v>588</v>
+        <v>800</v>
       </c>
       <c r="G54" s="0" t="s">
-        <v>618</v>
+        <v>830</v>
       </c>
       <c r="H54" s="0">
-        <v>19044117</v>
+        <v>10367491</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="0" t="s">
-        <v>463</v>
+        <v>666</v>
       </c>
       <c r="B55" s="0" t="s">
-        <v>278</v>
+        <v>712</v>
       </c>
       <c r="C55" s="0">
         <v>2100</v>
@@ -5700,24 +8122,24 @@
         <v>107</v>
       </c>
       <c r="E55" s="0" t="s">
-        <v>550</v>
+        <v>756</v>
       </c>
       <c r="F55" s="0" t="s">
-        <v>588</v>
+        <v>800</v>
       </c>
       <c r="G55" s="0" t="s">
-        <v>618</v>
+        <v>830</v>
       </c>
       <c r="H55" s="0">
-        <v>19044118</v>
+        <v>10367492</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="0" t="s">
-        <v>464</v>
+        <v>667</v>
       </c>
       <c r="B56" s="0" t="s">
-        <v>503</v>
+        <v>277</v>
       </c>
       <c r="C56" s="0">
         <v>1100</v>
@@ -5726,24 +8148,24 @@
         <v>107</v>
       </c>
       <c r="E56" s="0" t="s">
-        <v>551</v>
+        <v>757</v>
       </c>
       <c r="F56" s="0" t="s">
-        <v>593</v>
+        <v>796</v>
       </c>
       <c r="G56" s="0" t="s">
-        <v>622</v>
+        <v>827</v>
       </c>
       <c r="H56" s="0">
-        <v>19926542</v>
+        <v>19044117</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="0" t="s">
-        <v>464</v>
+        <v>667</v>
       </c>
       <c r="B57" s="0" t="s">
-        <v>504</v>
+        <v>278</v>
       </c>
       <c r="C57" s="0">
         <v>2100</v>
@@ -5752,76 +8174,76 @@
         <v>107</v>
       </c>
       <c r="E57" s="0" t="s">
-        <v>551</v>
+        <v>757</v>
       </c>
       <c r="F57" s="0" t="s">
-        <v>593</v>
+        <v>796</v>
       </c>
       <c r="G57" s="0" t="s">
-        <v>623</v>
+        <v>827</v>
       </c>
       <c r="H57" s="0">
-        <v>19926545</v>
+        <v>19044118</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="0" t="s">
-        <v>464</v>
+        <v>668</v>
       </c>
       <c r="B58" s="0" t="s">
-        <v>505</v>
+        <v>340</v>
       </c>
       <c r="C58" s="0">
-        <v>2100</v>
+        <v>1100</v>
       </c>
       <c r="D58" s="0">
         <v>107</v>
       </c>
       <c r="E58" s="0" t="s">
-        <v>552</v>
+        <v>758</v>
       </c>
       <c r="F58" s="0" t="s">
-        <v>594</v>
+        <v>801</v>
       </c>
       <c r="G58" s="0" t="s">
-        <v>624</v>
+        <v>831</v>
       </c>
       <c r="H58" s="0">
-        <v>19926541</v>
+        <v>11111111</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="0" t="s">
-        <v>464</v>
+        <v>668</v>
       </c>
       <c r="B59" s="0" t="s">
-        <v>506</v>
+        <v>339</v>
       </c>
       <c r="C59" s="0">
-        <v>1100</v>
+        <v>2100</v>
       </c>
       <c r="D59" s="0">
         <v>107</v>
       </c>
       <c r="E59" s="0" t="s">
-        <v>552</v>
+        <v>758</v>
       </c>
       <c r="F59" s="0" t="s">
-        <v>594</v>
+        <v>801</v>
       </c>
       <c r="G59" s="0" t="s">
-        <v>623</v>
+        <v>831</v>
       </c>
       <c r="H59" s="0">
-        <v>19926543</v>
+        <v>11111111</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="0" t="s">
-        <v>465</v>
+        <v>669</v>
       </c>
       <c r="B60" s="0" t="s">
-        <v>277</v>
+        <v>713</v>
       </c>
       <c r="C60" s="0">
         <v>1100</v>
@@ -5830,24 +8252,24 @@
         <v>107</v>
       </c>
       <c r="E60" s="0" t="s">
-        <v>553</v>
+        <v>759</v>
       </c>
       <c r="F60" s="0" t="s">
-        <v>353</v>
+        <v>802</v>
       </c>
       <c r="G60" s="0" t="s">
-        <v>608</v>
+        <v>832</v>
       </c>
       <c r="H60" s="0">
-        <v>677155</v>
+        <v>19926542</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="0" t="s">
-        <v>465</v>
+        <v>669</v>
       </c>
       <c r="B61" s="0" t="s">
-        <v>278</v>
+        <v>714</v>
       </c>
       <c r="C61" s="0">
         <v>2100</v>
@@ -5856,76 +8278,76 @@
         <v>107</v>
       </c>
       <c r="E61" s="0" t="s">
-        <v>554</v>
+        <v>759</v>
       </c>
       <c r="F61" s="0" t="s">
-        <v>353</v>
+        <v>802</v>
       </c>
       <c r="G61" s="0" t="s">
-        <v>608</v>
+        <v>833</v>
       </c>
       <c r="H61" s="0">
-        <v>677154</v>
+        <v>19926545</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="0" t="s">
-        <v>466</v>
+        <v>669</v>
       </c>
       <c r="B62" s="0" t="s">
-        <v>277</v>
+        <v>715</v>
       </c>
       <c r="C62" s="0">
-        <v>1100</v>
+        <v>2100</v>
       </c>
       <c r="D62" s="0">
         <v>107</v>
       </c>
       <c r="E62" s="0" t="s">
-        <v>555</v>
+        <v>760</v>
       </c>
       <c r="F62" s="0" t="s">
-        <v>595</v>
+        <v>803</v>
       </c>
       <c r="G62" s="0" t="s">
-        <v>616</v>
+        <v>834</v>
       </c>
       <c r="H62" s="0">
-        <v>19982207</v>
+        <v>19926541</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="0" t="s">
-        <v>466</v>
+        <v>669</v>
       </c>
       <c r="B63" s="0" t="s">
-        <v>278</v>
+        <v>716</v>
       </c>
       <c r="C63" s="0">
-        <v>2100</v>
+        <v>1100</v>
       </c>
       <c r="D63" s="0">
         <v>107</v>
       </c>
       <c r="E63" s="0" t="s">
-        <v>555</v>
+        <v>760</v>
       </c>
       <c r="F63" s="0" t="s">
-        <v>595</v>
+        <v>803</v>
       </c>
       <c r="G63" s="0" t="s">
-        <v>616</v>
+        <v>833</v>
       </c>
       <c r="H63" s="0">
-        <v>19982210</v>
+        <v>19926543</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="0" t="s">
-        <v>467</v>
+        <v>670</v>
       </c>
       <c r="B64" s="0" t="s">
-        <v>488</v>
+        <v>277</v>
       </c>
       <c r="C64" s="0">
         <v>1100</v>
@@ -5934,24 +8356,24 @@
         <v>107</v>
       </c>
       <c r="E64" s="0" t="s">
-        <v>556</v>
+        <v>761</v>
       </c>
       <c r="F64" s="0" t="s">
-        <v>583</v>
+        <v>353</v>
       </c>
       <c r="G64" s="0" t="s">
-        <v>615</v>
+        <v>817</v>
       </c>
       <c r="H64" s="0">
-        <v>18748228</v>
+        <v>677155</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="0" t="s">
-        <v>467</v>
+        <v>670</v>
       </c>
       <c r="B65" s="0" t="s">
-        <v>489</v>
+        <v>278</v>
       </c>
       <c r="C65" s="0">
         <v>2100</v>
@@ -5960,24 +8382,24 @@
         <v>107</v>
       </c>
       <c r="E65" s="0" t="s">
-        <v>557</v>
+        <v>762</v>
       </c>
       <c r="F65" s="0" t="s">
-        <v>583</v>
+        <v>353</v>
       </c>
       <c r="G65" s="0" t="s">
-        <v>615</v>
+        <v>817</v>
       </c>
       <c r="H65" s="0">
-        <v>18748229</v>
+        <v>677154</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="0" t="s">
-        <v>467</v>
+        <v>671</v>
       </c>
       <c r="B66" s="0" t="s">
-        <v>507</v>
+        <v>277</v>
       </c>
       <c r="C66" s="0">
         <v>1100</v>
@@ -5986,24 +8408,24 @@
         <v>107</v>
       </c>
       <c r="E66" s="0" t="s">
-        <v>558</v>
+        <v>763</v>
       </c>
       <c r="F66" s="0" t="s">
-        <v>596</v>
+        <v>804</v>
       </c>
       <c r="G66" s="0" t="s">
-        <v>603</v>
+        <v>825</v>
       </c>
       <c r="H66" s="0">
-        <v>19623813</v>
+        <v>19982207</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="0" t="s">
-        <v>467</v>
+        <v>671</v>
       </c>
       <c r="B67" s="0" t="s">
-        <v>508</v>
+        <v>278</v>
       </c>
       <c r="C67" s="0">
         <v>2100</v>
@@ -6012,123 +8434,125 @@
         <v>107</v>
       </c>
       <c r="E67" s="0" t="s">
-        <v>559</v>
+        <v>763</v>
       </c>
       <c r="F67" s="0" t="s">
-        <v>596</v>
+        <v>804</v>
       </c>
       <c r="G67" s="0" t="s">
-        <v>603</v>
+        <v>825</v>
       </c>
       <c r="H67" s="0">
-        <v>19623814</v>
+        <v>19982210</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="0" t="s">
-        <v>468</v>
+        <v>672</v>
       </c>
       <c r="B68" s="0" t="s">
-        <v>277</v>
+        <v>694</v>
       </c>
       <c r="C68" s="0">
         <v>1100</v>
       </c>
       <c r="D68" s="0">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="E68" s="0" t="s">
-        <v>560</v>
+        <v>764</v>
       </c>
       <c r="F68" s="0" t="s">
-        <v>582</v>
+        <v>790</v>
       </c>
       <c r="G68" s="0" t="s">
-        <v>608</v>
+        <v>824</v>
       </c>
       <c r="H68" s="0">
-        <v>677164</v>
+        <v>18748228</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="0" t="s">
-        <v>468</v>
+        <v>672</v>
       </c>
       <c r="B69" s="0" t="s">
-        <v>278</v>
+        <v>695</v>
       </c>
       <c r="C69" s="0">
         <v>2100</v>
       </c>
       <c r="D69" s="0">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="E69" s="0" t="s">
-        <v>560</v>
+        <v>764</v>
       </c>
       <c r="F69" s="0" t="s">
-        <v>582</v>
+        <v>790</v>
       </c>
       <c r="G69" s="0" t="s">
-        <v>608</v>
+        <v>824</v>
       </c>
       <c r="H69" s="0">
-        <v>677112</v>
+        <v>18748229</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="0" t="s">
-        <v>468</v>
+        <v>672</v>
       </c>
       <c r="B70" s="0" t="s">
-        <v>509</v>
+        <v>717</v>
       </c>
       <c r="C70" s="0">
-        <v>2200</v>
+        <v>1100</v>
       </c>
       <c r="D70" s="0">
         <v>107</v>
       </c>
-      <c r="E70" s="0"/>
+      <c r="E70" s="0" t="s">
+        <v>765</v>
+      </c>
       <c r="F70" s="0" t="s">
-        <v>582</v>
+        <v>805</v>
       </c>
       <c r="G70" s="0" t="s">
-        <v>608</v>
+        <v>812</v>
       </c>
       <c r="H70" s="0">
-        <v>9271975</v>
+        <v>19623813</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="0" t="s">
-        <v>468</v>
+        <v>672</v>
       </c>
       <c r="B71" s="0" t="s">
-        <v>510</v>
+        <v>718</v>
       </c>
       <c r="C71" s="0">
-        <v>3400</v>
+        <v>2100</v>
       </c>
       <c r="D71" s="0">
         <v>107</v>
       </c>
       <c r="E71" s="0" t="s">
-        <v>561</v>
+        <v>765</v>
       </c>
       <c r="F71" s="0" t="s">
-        <v>597</v>
+        <v>805</v>
       </c>
       <c r="G71" s="0" t="s">
-        <v>625</v>
+        <v>812</v>
       </c>
       <c r="H71" s="0">
-        <v>19869294</v>
+        <v>19623814</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="0" t="s">
-        <v>469</v>
+        <v>673</v>
       </c>
       <c r="B72" s="0" t="s">
         <v>277</v>
@@ -6140,21 +8564,21 @@
         <v>107</v>
       </c>
       <c r="E72" s="0" t="s">
-        <v>562</v>
+        <v>766</v>
       </c>
       <c r="F72" s="0" t="s">
-        <v>575</v>
+        <v>789</v>
       </c>
       <c r="G72" s="0" t="s">
-        <v>603</v>
+        <v>817</v>
       </c>
       <c r="H72" s="0">
-        <v>677142</v>
+        <v>677164</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="0" t="s">
-        <v>469</v>
+        <v>673</v>
       </c>
       <c r="B73" s="0" t="s">
         <v>278</v>
@@ -6166,73 +8590,73 @@
         <v>107</v>
       </c>
       <c r="E73" s="0" t="s">
-        <v>562</v>
+        <v>766</v>
       </c>
       <c r="F73" s="0" t="s">
-        <v>575</v>
+        <v>789</v>
       </c>
       <c r="G73" s="0" t="s">
-        <v>603</v>
+        <v>817</v>
       </c>
       <c r="H73" s="0">
-        <v>677167</v>
+        <v>677112</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="0" t="s">
-        <v>470</v>
+        <v>673</v>
       </c>
       <c r="B74" s="0" t="s">
-        <v>277</v>
+        <v>719</v>
       </c>
       <c r="C74" s="0">
-        <v>1100</v>
+        <v>2200</v>
       </c>
       <c r="D74" s="0">
         <v>107</v>
       </c>
       <c r="E74" s="0" t="s">
-        <v>537</v>
+        <v>766</v>
       </c>
       <c r="F74" s="0" t="s">
-        <v>579</v>
+        <v>789</v>
       </c>
       <c r="G74" s="0" t="s">
-        <v>611</v>
+        <v>817</v>
       </c>
       <c r="H74" s="0">
-        <v>18905784</v>
+        <v>9271975</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="0" t="s">
-        <v>470</v>
+        <v>673</v>
       </c>
       <c r="B75" s="0" t="s">
-        <v>278</v>
+        <v>720</v>
       </c>
       <c r="C75" s="0">
-        <v>2100</v>
+        <v>3400</v>
       </c>
       <c r="D75" s="0">
         <v>107</v>
       </c>
       <c r="E75" s="0" t="s">
-        <v>537</v>
+        <v>767</v>
       </c>
       <c r="F75" s="0" t="s">
-        <v>579</v>
+        <v>806</v>
       </c>
       <c r="G75" s="0" t="s">
-        <v>611</v>
+        <v>835</v>
       </c>
       <c r="H75" s="0">
-        <v>18905783</v>
+        <v>19869294</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="0" t="s">
-        <v>471</v>
+        <v>674</v>
       </c>
       <c r="B76" s="0" t="s">
         <v>277</v>
@@ -6244,21 +8668,21 @@
         <v>107</v>
       </c>
       <c r="E76" s="0" t="s">
-        <v>563</v>
+        <v>768</v>
       </c>
       <c r="F76" s="0" t="s">
-        <v>585</v>
+        <v>782</v>
       </c>
       <c r="G76" s="0" t="s">
-        <v>626</v>
+        <v>812</v>
       </c>
       <c r="H76" s="0">
-        <v>18866323</v>
+        <v>677142</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="0" t="s">
-        <v>471</v>
+        <v>674</v>
       </c>
       <c r="B77" s="0" t="s">
         <v>278</v>
@@ -6270,206 +8694,206 @@
         <v>107</v>
       </c>
       <c r="E77" s="0" t="s">
-        <v>564</v>
+        <v>768</v>
       </c>
       <c r="F77" s="0" t="s">
-        <v>585</v>
+        <v>782</v>
       </c>
       <c r="G77" s="0" t="s">
-        <v>626</v>
+        <v>812</v>
       </c>
       <c r="H77" s="0">
-        <v>18866324</v>
+        <v>677167</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="0" t="s">
-        <v>472</v>
+        <v>675</v>
       </c>
       <c r="B78" s="0" t="s">
-        <v>511</v>
+        <v>277</v>
       </c>
       <c r="C78" s="0">
-        <v>3400</v>
+        <v>1100</v>
       </c>
       <c r="D78" s="0">
         <v>107</v>
       </c>
       <c r="E78" s="0" t="s">
-        <v>565</v>
+        <v>747</v>
       </c>
       <c r="F78" s="0" t="s">
-        <v>598</v>
+        <v>786</v>
       </c>
       <c r="G78" s="0" t="s">
-        <v>627</v>
+        <v>820</v>
       </c>
       <c r="H78" s="0">
-        <v>19032282</v>
+        <v>18905784</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="0" t="s">
-        <v>473</v>
+        <v>675</v>
       </c>
       <c r="B79" s="0" t="s">
-        <v>512</v>
+        <v>278</v>
       </c>
       <c r="C79" s="0">
-        <v>1100</v>
+        <v>2100</v>
       </c>
       <c r="D79" s="0">
         <v>107</v>
       </c>
       <c r="E79" s="0" t="s">
-        <v>566</v>
+        <v>747</v>
       </c>
       <c r="F79" s="0" t="s">
-        <v>599</v>
+        <v>786</v>
       </c>
       <c r="G79" s="0" t="s">
-        <v>609</v>
+        <v>820</v>
       </c>
       <c r="H79" s="0">
-        <v>6737411</v>
+        <v>18905783</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="0" t="s">
-        <v>473</v>
+        <v>676</v>
       </c>
       <c r="B80" s="0" t="s">
-        <v>513</v>
+        <v>277</v>
       </c>
       <c r="C80" s="0">
-        <v>2100</v>
+        <v>1100</v>
       </c>
       <c r="D80" s="0">
         <v>107</v>
       </c>
       <c r="E80" s="0" t="s">
-        <v>566</v>
+        <v>769</v>
       </c>
       <c r="F80" s="0" t="s">
-        <v>599</v>
+        <v>792</v>
       </c>
       <c r="G80" s="0" t="s">
-        <v>609</v>
+        <v>836</v>
       </c>
       <c r="H80" s="0">
-        <v>6737412</v>
+        <v>18866323</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="0" t="s">
-        <v>473</v>
+        <v>676</v>
       </c>
       <c r="B81" s="0" t="s">
-        <v>514</v>
+        <v>278</v>
       </c>
       <c r="C81" s="0">
-        <v>1100</v>
+        <v>2100</v>
       </c>
       <c r="D81" s="0">
         <v>107</v>
       </c>
       <c r="E81" s="0" t="s">
-        <v>566</v>
+        <v>770</v>
       </c>
       <c r="F81" s="0" t="s">
-        <v>600</v>
+        <v>792</v>
       </c>
       <c r="G81" s="0" t="s">
-        <v>609</v>
+        <v>836</v>
       </c>
       <c r="H81" s="0">
-        <v>6737413</v>
+        <v>18866324</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="0" t="s">
-        <v>473</v>
+        <v>677</v>
       </c>
       <c r="B82" s="0" t="s">
-        <v>515</v>
+        <v>277</v>
       </c>
       <c r="C82" s="0">
-        <v>2100</v>
+        <v>1100</v>
       </c>
       <c r="D82" s="0">
         <v>107</v>
       </c>
       <c r="E82" s="0" t="s">
-        <v>566</v>
+        <v>771</v>
       </c>
       <c r="F82" s="0" t="s">
-        <v>600</v>
+        <v>804</v>
       </c>
       <c r="G82" s="0" t="s">
-        <v>609</v>
+        <v>825</v>
       </c>
       <c r="H82" s="0">
-        <v>6737414</v>
+        <v>11111111</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="0" t="s">
-        <v>474</v>
+        <v>677</v>
       </c>
       <c r="B83" s="0" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C83" s="0">
-        <v>1100</v>
+        <v>2100</v>
       </c>
       <c r="D83" s="0">
         <v>107</v>
       </c>
       <c r="E83" s="0" t="s">
-        <v>567</v>
+        <v>771</v>
       </c>
       <c r="F83" s="0" t="s">
-        <v>601</v>
+        <v>804</v>
       </c>
       <c r="G83" s="0" t="s">
-        <v>612</v>
+        <v>825</v>
       </c>
       <c r="H83" s="0">
-        <v>18771406</v>
+        <v>11111111</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="0" t="s">
-        <v>474</v>
+        <v>678</v>
       </c>
       <c r="B84" s="0" t="s">
-        <v>278</v>
+        <v>721</v>
       </c>
       <c r="C84" s="0">
-        <v>2100</v>
+        <v>3400</v>
       </c>
       <c r="D84" s="0">
         <v>107</v>
       </c>
       <c r="E84" s="0" t="s">
-        <v>567</v>
+        <v>772</v>
       </c>
       <c r="F84" s="0" t="s">
-        <v>601</v>
+        <v>807</v>
       </c>
       <c r="G84" s="0" t="s">
-        <v>612</v>
+        <v>837</v>
       </c>
       <c r="H84" s="0">
-        <v>18771407</v>
+        <v>19032282</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="0" t="s">
-        <v>475</v>
+        <v>679</v>
       </c>
       <c r="B85" s="0" t="s">
-        <v>277</v>
+        <v>722</v>
       </c>
       <c r="C85" s="0">
         <v>1100</v>
@@ -6478,24 +8902,24 @@
         <v>107</v>
       </c>
       <c r="E85" s="0" t="s">
-        <v>568</v>
+        <v>773</v>
       </c>
       <c r="F85" s="0" t="s">
-        <v>602</v>
+        <v>808</v>
       </c>
       <c r="G85" s="0" t="s">
-        <v>606</v>
+        <v>818</v>
       </c>
       <c r="H85" s="0">
-        <v>19479016</v>
+        <v>6737411</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="0" t="s">
-        <v>475</v>
+        <v>679</v>
       </c>
       <c r="B86" s="0" t="s">
-        <v>278</v>
+        <v>723</v>
       </c>
       <c r="C86" s="0">
         <v>2100</v>
@@ -6504,24 +8928,24 @@
         <v>107</v>
       </c>
       <c r="E86" s="0" t="s">
-        <v>568</v>
+        <v>773</v>
       </c>
       <c r="F86" s="0" t="s">
-        <v>602</v>
+        <v>808</v>
       </c>
       <c r="G86" s="0" t="s">
-        <v>606</v>
+        <v>818</v>
       </c>
       <c r="H86" s="0">
-        <v>19479015</v>
+        <v>6737412</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="0" t="s">
-        <v>476</v>
+        <v>679</v>
       </c>
       <c r="B87" s="0" t="s">
-        <v>277</v>
+        <v>724</v>
       </c>
       <c r="C87" s="0">
         <v>1100</v>
@@ -6530,24 +8954,24 @@
         <v>107</v>
       </c>
       <c r="E87" s="0" t="s">
-        <v>569</v>
+        <v>773</v>
       </c>
       <c r="F87" s="0" t="s">
-        <v>579</v>
+        <v>809</v>
       </c>
       <c r="G87" s="0" t="s">
-        <v>611</v>
+        <v>818</v>
       </c>
       <c r="H87" s="0">
-        <v>18905786</v>
+        <v>6737413</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="0" t="s">
-        <v>476</v>
+        <v>679</v>
       </c>
       <c r="B88" s="0" t="s">
-        <v>278</v>
+        <v>725</v>
       </c>
       <c r="C88" s="0">
         <v>2100</v>
@@ -6556,15 +8980,171 @@
         <v>107</v>
       </c>
       <c r="E88" s="0" t="s">
-        <v>569</v>
+        <v>773</v>
       </c>
       <c r="F88" s="0" t="s">
-        <v>579</v>
+        <v>809</v>
       </c>
       <c r="G88" s="0" t="s">
-        <v>611</v>
+        <v>818</v>
       </c>
       <c r="H88" s="0">
+        <v>6737414</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="0" t="s">
+        <v>680</v>
+      </c>
+      <c r="B89" s="0" t="s">
+        <v>277</v>
+      </c>
+      <c r="C89" s="0">
+        <v>1100</v>
+      </c>
+      <c r="D89" s="0">
+        <v>107</v>
+      </c>
+      <c r="E89" s="0" t="s">
+        <v>774</v>
+      </c>
+      <c r="F89" s="0" t="s">
+        <v>810</v>
+      </c>
+      <c r="G89" s="0" t="s">
+        <v>821</v>
+      </c>
+      <c r="H89" s="0">
+        <v>18771406</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="0" t="s">
+        <v>680</v>
+      </c>
+      <c r="B90" s="0" t="s">
+        <v>278</v>
+      </c>
+      <c r="C90" s="0">
+        <v>2100</v>
+      </c>
+      <c r="D90" s="0">
+        <v>107</v>
+      </c>
+      <c r="E90" s="0" t="s">
+        <v>774</v>
+      </c>
+      <c r="F90" s="0" t="s">
+        <v>810</v>
+      </c>
+      <c r="G90" s="0" t="s">
+        <v>821</v>
+      </c>
+      <c r="H90" s="0">
+        <v>18771407</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="0" t="s">
+        <v>681</v>
+      </c>
+      <c r="B91" s="0" t="s">
+        <v>277</v>
+      </c>
+      <c r="C91" s="0">
+        <v>1100</v>
+      </c>
+      <c r="D91" s="0">
+        <v>107</v>
+      </c>
+      <c r="E91" s="0" t="s">
+        <v>775</v>
+      </c>
+      <c r="F91" s="0" t="s">
+        <v>811</v>
+      </c>
+      <c r="G91" s="0" t="s">
+        <v>815</v>
+      </c>
+      <c r="H91" s="0">
+        <v>19479016</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="0" t="s">
+        <v>681</v>
+      </c>
+      <c r="B92" s="0" t="s">
+        <v>278</v>
+      </c>
+      <c r="C92" s="0">
+        <v>2100</v>
+      </c>
+      <c r="D92" s="0">
+        <v>107</v>
+      </c>
+      <c r="E92" s="0" t="s">
+        <v>775</v>
+      </c>
+      <c r="F92" s="0" t="s">
+        <v>811</v>
+      </c>
+      <c r="G92" s="0" t="s">
+        <v>815</v>
+      </c>
+      <c r="H92" s="0">
+        <v>19479015</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="0" t="s">
+        <v>682</v>
+      </c>
+      <c r="B93" s="0" t="s">
+        <v>277</v>
+      </c>
+      <c r="C93" s="0">
+        <v>1100</v>
+      </c>
+      <c r="D93" s="0">
+        <v>107</v>
+      </c>
+      <c r="E93" s="0" t="s">
+        <v>776</v>
+      </c>
+      <c r="F93" s="0" t="s">
+        <v>786</v>
+      </c>
+      <c r="G93" s="0" t="s">
+        <v>820</v>
+      </c>
+      <c r="H93" s="0">
+        <v>18905786</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="0" t="s">
+        <v>682</v>
+      </c>
+      <c r="B94" s="0" t="s">
+        <v>278</v>
+      </c>
+      <c r="C94" s="0">
+        <v>2100</v>
+      </c>
+      <c r="D94" s="0">
+        <v>107</v>
+      </c>
+      <c r="E94" s="0" t="s">
+        <v>776</v>
+      </c>
+      <c r="F94" s="0" t="s">
+        <v>786</v>
+      </c>
+      <c r="G94" s="0" t="s">
+        <v>820</v>
+      </c>
+      <c r="H94" s="0">
         <v>18905785</v>
       </c>
     </row>
